--- a/outputs/forecast_education_by_tract.xlsx
+++ b/outputs/forecast_education_by_tract.xlsx
@@ -412,7 +412,7 @@
         <v>2026</v>
       </c>
       <c r="D4">
-        <v>58.39810922844998</v>
+        <v>57.76747169861494</v>
       </c>
     </row>
     <row r="5">
@@ -425,7 +425,7 @@
         <v>2027</v>
       </c>
       <c r="D5">
-        <v>58.3694764097058</v>
+        <v>58.30013819965454</v>
       </c>
     </row>
     <row r="6">
@@ -438,7 +438,7 @@
         <v>2028</v>
       </c>
       <c r="D6">
-        <v>57.73626084527123</v>
+        <v>57.14117263754419</v>
       </c>
     </row>
     <row r="7">
@@ -477,7 +477,7 @@
         <v>2026</v>
       </c>
       <c r="D9">
-        <v>58.66478375667332</v>
+        <v>59.70762697363843</v>
       </c>
     </row>
     <row r="10">
@@ -490,7 +490,7 @@
         <v>2027</v>
       </c>
       <c r="D10">
-        <v>59.7102229813049</v>
+        <v>60.74658991993564</v>
       </c>
     </row>
     <row r="11">
@@ -503,7 +503,7 @@
         <v>2028</v>
       </c>
       <c r="D11">
-        <v>60.74601234998442</v>
+        <v>61.78382015637917</v>
       </c>
     </row>
     <row r="12">
@@ -542,7 +542,7 @@
         <v>2026</v>
       </c>
       <c r="D14">
-        <v>55.55996615237019</v>
+        <v>59.2867902118268</v>
       </c>
     </row>
     <row r="15">
@@ -555,7 +555,7 @@
         <v>2027</v>
       </c>
       <c r="D15">
-        <v>59.07526050579042</v>
+        <v>62.09130228774994</v>
       </c>
     </row>
     <row r="16">
@@ -568,7 +568,7 @@
         <v>2028</v>
       </c>
       <c r="D16">
-        <v>61.93578869493956</v>
+        <v>64.42927358524194</v>
       </c>
     </row>
     <row r="17">
@@ -607,7 +607,7 @@
         <v>2026</v>
       </c>
       <c r="D19">
-        <v>48.70878547435618</v>
+        <v>51.04356535743842</v>
       </c>
     </row>
     <row r="20">
@@ -620,7 +620,7 @@
         <v>2027</v>
       </c>
       <c r="D20">
-        <v>50.02865261476517</v>
+        <v>51.61339927477216</v>
       </c>
     </row>
     <row r="21">
@@ -633,7 +633,7 @@
         <v>2028</v>
       </c>
       <c r="D21">
-        <v>52.41825480141249</v>
+        <v>54.59779977202689</v>
       </c>
     </row>
     <row r="22">
@@ -672,7 +672,7 @@
         <v>2026</v>
       </c>
       <c r="D24">
-        <v>75.5927291533782</v>
+        <v>76.90891498382292</v>
       </c>
     </row>
     <row r="25">
@@ -685,7 +685,7 @@
         <v>2027</v>
       </c>
       <c r="D25">
-        <v>76.90615324198905</v>
+        <v>78.23044542843377</v>
       </c>
     </row>
     <row r="26">
@@ -698,7 +698,7 @@
         <v>2028</v>
       </c>
       <c r="D26">
-        <v>78.23100502547548</v>
+        <v>79.55365466416973</v>
       </c>
     </row>
     <row r="27">
@@ -737,7 +737,7 @@
         <v>2026</v>
       </c>
       <c r="D29">
-        <v>51.83694986964647</v>
+        <v>52.54720381146964</v>
       </c>
     </row>
     <row r="30">
@@ -750,7 +750,7 @@
         <v>2027</v>
       </c>
       <c r="D30">
-        <v>52.54713070315618</v>
+        <v>53.25885183001714</v>
       </c>
     </row>
     <row r="31">
@@ -763,7 +763,7 @@
         <v>2028</v>
       </c>
       <c r="D31">
-        <v>53.25885514278519</v>
+        <v>53.9705097868688</v>
       </c>
     </row>
     <row r="32">
@@ -802,7 +802,7 @@
         <v>2026</v>
       </c>
       <c r="D34">
-        <v>35.31871330739799</v>
+        <v>34.69589621673024</v>
       </c>
     </row>
     <row r="35">
@@ -815,7 +815,7 @@
         <v>2027</v>
       </c>
       <c r="D35">
-        <v>34.69364056452255</v>
+        <v>34.05535138344166</v>
       </c>
     </row>
     <row r="36">
@@ -828,7 +828,7 @@
         <v>2028</v>
       </c>
       <c r="D36">
-        <v>34.0548871861767</v>
+        <v>33.41341395835819</v>
       </c>
     </row>
     <row r="37">
@@ -867,7 +867,7 @@
         <v>2026</v>
       </c>
       <c r="D39">
-        <v>69.50012875014977</v>
+        <v>70.66172570309961</v>
       </c>
     </row>
     <row r="40">
@@ -880,7 +880,7 @@
         <v>2027</v>
       </c>
       <c r="D40">
-        <v>70.66172767360341</v>
+        <v>71.82317578895653</v>
       </c>
     </row>
     <row r="41">
@@ -893,7 +893,7 @@
         <v>2028</v>
       </c>
       <c r="D41">
-        <v>71.82317576354143</v>
+        <v>72.98462579856813</v>
       </c>
     </row>
     <row r="42">
@@ -932,7 +932,7 @@
         <v>2026</v>
       </c>
       <c r="D44">
-        <v>75.25792769494005</v>
+        <v>77.87363823946833</v>
       </c>
     </row>
     <row r="45">
@@ -945,7 +945,7 @@
         <v>2027</v>
       </c>
       <c r="D45">
-        <v>78.06604480854283</v>
+        <v>80.81195089878346</v>
       </c>
     </row>
     <row r="46">
@@ -958,7 +958,7 @@
         <v>2028</v>
       </c>
       <c r="D46">
-        <v>80.66655525872285</v>
+        <v>83.31407663791674</v>
       </c>
     </row>
     <row r="47">
@@ -997,7 +997,7 @@
         <v>2026</v>
       </c>
       <c r="D49">
-        <v>36.64126022680107</v>
+        <v>35.80783891725254</v>
       </c>
     </row>
     <row r="50">
@@ -1010,7 +1010,7 @@
         <v>2027</v>
       </c>
       <c r="D50">
-        <v>36.02878016062464</v>
+        <v>35.36626365864096</v>
       </c>
     </row>
     <row r="51">
@@ -1023,7 +1023,7 @@
         <v>2028</v>
       </c>
       <c r="D51">
-        <v>35.1861195479871</v>
+        <v>34.3842560680678</v>
       </c>
     </row>
     <row r="52">
@@ -1062,7 +1062,7 @@
         <v>2026</v>
       </c>
       <c r="D54">
-        <v>32.71540989654771</v>
+        <v>32.18321209961779</v>
       </c>
     </row>
     <row r="55">
@@ -1075,7 +1075,7 @@
         <v>2027</v>
       </c>
       <c r="D55">
-        <v>32.18321212643073</v>
+        <v>31.65100571128662</v>
       </c>
     </row>
     <row r="56">
@@ -1088,7 +1088,7 @@
         <v>2028</v>
       </c>
       <c r="D56">
-        <v>31.65100571120372</v>
+        <v>31.11879932270674</v>
       </c>
     </row>
     <row r="57">
@@ -1127,7 +1127,7 @@
         <v>2026</v>
       </c>
       <c r="D59">
-        <v>35.58652826916175</v>
+        <v>36.53192294183476</v>
       </c>
     </row>
     <row r="60">
@@ -1140,7 +1140,7 @@
         <v>2027</v>
       </c>
       <c r="D60">
-        <v>36.37933220165538</v>
+        <v>37.21729269202313</v>
       </c>
     </row>
     <row r="61">
@@ -1153,7 +1153,7 @@
         <v>2028</v>
       </c>
       <c r="D61">
-        <v>37.33503859407936</v>
+        <v>38.25590014838018</v>
       </c>
     </row>
     <row r="62">
@@ -1192,7 +1192,7 @@
         <v>2026</v>
       </c>
       <c r="D64">
-        <v>22.74607439916527</v>
+        <v>22.82378258062722</v>
       </c>
     </row>
     <row r="65">
@@ -1205,7 +1205,7 @@
         <v>2027</v>
       </c>
       <c r="D65">
-        <v>22.583460720576</v>
+        <v>22.57140008654042</v>
       </c>
     </row>
     <row r="66">
@@ -1218,7 +1218,7 @@
         <v>2028</v>
       </c>
       <c r="D66">
-        <v>22.71915732482323</v>
+        <v>22.76228930730206</v>
       </c>
     </row>
     <row r="67">
@@ -1257,7 +1257,7 @@
         <v>2026</v>
       </c>
       <c r="D69">
-        <v>22.51844078677589</v>
+        <v>23.73327159378967</v>
       </c>
     </row>
     <row r="70">
@@ -1270,7 +1270,7 @@
         <v>2027</v>
       </c>
       <c r="D70">
-        <v>23.73339534364773</v>
+        <v>24.94892614245602</v>
       </c>
     </row>
     <row r="71">
@@ -1283,7 +1283,7 @@
         <v>2028</v>
       </c>
       <c r="D71">
-        <v>24.94895998620292</v>
+        <v>26.16468222236304</v>
       </c>
     </row>
     <row r="72">
@@ -1322,7 +1322,7 @@
         <v>2026</v>
       </c>
       <c r="D74">
-        <v>40.45231242233928</v>
+        <v>40.76501381009898</v>
       </c>
     </row>
     <row r="75">
@@ -1335,7 +1335,7 @@
         <v>2027</v>
       </c>
       <c r="D75">
-        <v>40.76726434899928</v>
+        <v>41.07660785581011</v>
       </c>
     </row>
     <row r="76">
@@ -1348,7 +1348,7 @@
         <v>2028</v>
       </c>
       <c r="D76">
-        <v>41.07596337789602</v>
+        <v>41.38626846777898</v>
       </c>
     </row>
     <row r="77">
@@ -1387,7 +1387,7 @@
         <v>2026</v>
       </c>
       <c r="D79">
-        <v>22.23434547033054</v>
+        <v>22.61769203775646</v>
       </c>
     </row>
     <row r="80">
@@ -1400,7 +1400,7 @@
         <v>2027</v>
       </c>
       <c r="D80">
-        <v>23.18866889566472</v>
+        <v>23.71601843018146</v>
       </c>
     </row>
     <row r="81">
@@ -1413,7 +1413,7 @@
         <v>2028</v>
       </c>
       <c r="D81">
-        <v>23.38933440025004</v>
+        <v>23.83429273281219</v>
       </c>
     </row>
     <row r="82">
@@ -1452,7 +1452,7 @@
         <v>2026</v>
       </c>
       <c r="D84">
-        <v>28.05031271905068</v>
+        <v>27.2755068941876</v>
       </c>
     </row>
     <row r="85">
@@ -1465,7 +1465,7 @@
         <v>2027</v>
       </c>
       <c r="D85">
-        <v>27.2751307812498</v>
+        <v>26.49576819457291</v>
       </c>
     </row>
     <row r="86">
@@ -1478,7 +1478,7 @@
         <v>2028</v>
       </c>
       <c r="D86">
-        <v>26.49573101239241</v>
+        <v>25.71591794841672</v>
       </c>
     </row>
     <row r="87">
@@ -1517,7 +1517,7 @@
         <v>2026</v>
       </c>
       <c r="D89">
-        <v>47.19863487166415</v>
+        <v>48.92640144390523</v>
       </c>
     </row>
     <row r="90">
@@ -1530,7 +1530,7 @@
         <v>2027</v>
       </c>
       <c r="D90">
-        <v>48.93125819851705</v>
+        <v>50.6966980984205</v>
       </c>
     </row>
     <row r="91">
@@ -1543,7 +1543,7 @@
         <v>2028</v>
       </c>
       <c r="D91">
-        <v>50.69754173999889</v>
+        <v>52.46952567767096</v>
       </c>
     </row>
     <row r="92">
@@ -1582,7 +1582,7 @@
         <v>2026</v>
       </c>
       <c r="D94">
-        <v>31.77768079496542</v>
+        <v>32.63950411017432</v>
       </c>
     </row>
     <row r="95">
@@ -1595,7 +1595,7 @@
         <v>2027</v>
       </c>
       <c r="D95">
-        <v>32.6390910947234</v>
+        <v>33.50340109822172</v>
       </c>
     </row>
     <row r="96">
@@ -1608,7 +1608,7 @@
         <v>2028</v>
       </c>
       <c r="D96">
-        <v>33.50345259119558</v>
+        <v>34.36745256519067</v>
       </c>
     </row>
     <row r="97">
@@ -1647,7 +1647,7 @@
         <v>2026</v>
       </c>
       <c r="D99">
-        <v>57.2870078536647</v>
+        <v>58.5523750329042</v>
       </c>
     </row>
     <row r="100">
@@ -1660,7 +1660,7 @@
         <v>2027</v>
       </c>
       <c r="D100">
-        <v>58.55320613188521</v>
+        <v>59.8169761454695</v>
       </c>
     </row>
     <row r="101">
@@ -1673,7 +1673,7 @@
         <v>2028</v>
       </c>
       <c r="D101">
-        <v>59.81676422510793</v>
+        <v>61.0809414969501</v>
       </c>
     </row>
     <row r="102">
@@ -1712,7 +1712,7 @@
         <v>2026</v>
       </c>
       <c r="D104">
-        <v>37.87684408247249</v>
+        <v>36.59130564019921</v>
       </c>
     </row>
     <row r="105">
@@ -1725,7 +1725,7 @@
         <v>2027</v>
       </c>
       <c r="D105">
-        <v>36.58489135515035</v>
+        <v>35.25354486535836</v>
       </c>
     </row>
     <row r="106">
@@ -1738,7 +1738,7 @@
         <v>2028</v>
       </c>
       <c r="D106">
-        <v>35.25229733034855</v>
+        <v>33.91204148548809</v>
       </c>
     </row>
     <row r="107">
@@ -1777,7 +1777,7 @@
         <v>2026</v>
       </c>
       <c r="D109">
-        <v>69.99487923088824</v>
+        <v>71.78949136466628</v>
       </c>
     </row>
     <row r="110">
@@ -1790,7 +1790,7 @@
         <v>2027</v>
       </c>
       <c r="D110">
-        <v>71.78948859402692</v>
+        <v>73.58423680149552</v>
       </c>
     </row>
     <row r="111">
@@ -1803,7 +1803,7 @@
         <v>2028</v>
       </c>
       <c r="D111">
-        <v>73.58423685570195</v>
+        <v>75.37898240094407</v>
       </c>
     </row>
     <row r="112">
@@ -1842,7 +1842,7 @@
         <v>2026</v>
       </c>
       <c r="D114">
-        <v>37.02365732204832</v>
+        <v>38.64402667569625</v>
       </c>
     </row>
     <row r="115">
@@ -1855,7 +1855,7 @@
         <v>2027</v>
       </c>
       <c r="D115">
-        <v>38.64169085677546</v>
+        <v>40.27905219174654</v>
       </c>
     </row>
     <row r="116">
@@ -1868,7 +1868,7 @@
         <v>2028</v>
       </c>
       <c r="D116">
-        <v>40.2793040448644</v>
+        <v>41.91483326715039</v>
       </c>
     </row>
     <row r="117">
@@ -1907,7 +1907,7 @@
         <v>2026</v>
       </c>
       <c r="D119">
-        <v>64.82147152126929</v>
+        <v>65.57912859139748</v>
       </c>
     </row>
     <row r="120">
@@ -1920,7 +1920,7 @@
         <v>2027</v>
       </c>
       <c r="D120">
-        <v>65.51250621159861</v>
+        <v>66.32808592018924</v>
       </c>
     </row>
     <row r="121">
@@ -1933,7 +1933,7 @@
         <v>2028</v>
       </c>
       <c r="D121">
-        <v>66.35130400828955</v>
+        <v>67.14669751328188</v>
       </c>
     </row>
     <row r="122">
@@ -1972,7 +1972,7 @@
         <v>2026</v>
       </c>
       <c r="D124">
-        <v>72.83464993872421</v>
+        <v>72.90294167332866</v>
       </c>
     </row>
     <row r="125">
@@ -1985,7 +1985,7 @@
         <v>2027</v>
       </c>
       <c r="D125">
-        <v>72.89940848928023</v>
+        <v>72.98086689811075</v>
       </c>
     </row>
     <row r="126">
@@ -1998,7 +1998,7 @@
         <v>2028</v>
       </c>
       <c r="D126">
-        <v>72.98148387846005</v>
+        <v>73.06064306394079</v>
       </c>
     </row>
     <row r="127">
@@ -2037,7 +2037,7 @@
         <v>2026</v>
       </c>
       <c r="D129">
-        <v>48.6600472598241</v>
+        <v>48.6428574350251</v>
       </c>
     </row>
     <row r="130">
@@ -2050,7 +2050,7 @@
         <v>2027</v>
       </c>
       <c r="D130">
-        <v>48.63259638593016</v>
+        <v>48.57132906385727</v>
       </c>
     </row>
     <row r="131">
@@ -2063,7 +2063,7 @@
         <v>2028</v>
       </c>
       <c r="D131">
-        <v>48.56685921267143</v>
+        <v>48.48639113913191</v>
       </c>
     </row>
     <row r="132">
@@ -2102,7 +2102,7 @@
         <v>2026</v>
       </c>
       <c r="D134">
-        <v>40.98490762742998</v>
+        <v>40.94346642018658</v>
       </c>
     </row>
     <row r="135">
@@ -2115,7 +2115,7 @@
         <v>2027</v>
       </c>
       <c r="D135">
-        <v>40.94664156887375</v>
+        <v>40.90359833696518</v>
       </c>
     </row>
     <row r="136">
@@ -2128,7 +2128,7 @@
         <v>2028</v>
       </c>
       <c r="D136">
-        <v>40.90233058534049</v>
+        <v>40.85992699886972</v>
       </c>
     </row>
     <row r="137">
@@ -2167,7 +2167,7 @@
         <v>2026</v>
       </c>
       <c r="D139">
-        <v>71.62247112096223</v>
+        <v>74.30272533336549</v>
       </c>
     </row>
     <row r="140">
@@ -2180,7 +2180,7 @@
         <v>2027</v>
       </c>
       <c r="D140">
-        <v>74.45190334794371</v>
+        <v>77.20269514857402</v>
       </c>
     </row>
     <row r="141">
@@ -2193,7 +2193,7 @@
         <v>2028</v>
       </c>
       <c r="D141">
-        <v>77.10501174795591</v>
+        <v>79.80961476192822</v>
       </c>
     </row>
     <row r="142">
@@ -2232,7 +2232,7 @@
         <v>2026</v>
       </c>
       <c r="D144">
-        <v>36.50482335961454</v>
+        <v>40.62201440957546</v>
       </c>
     </row>
     <row r="145">
@@ -2245,7 +2245,7 @@
         <v>2027</v>
       </c>
       <c r="D145">
-        <v>40.6226790209318</v>
+        <v>44.73176561531885</v>
       </c>
     </row>
     <row r="146">
@@ -2258,7 +2258,7 @@
         <v>2028</v>
       </c>
       <c r="D146">
-        <v>44.73171879283439</v>
+        <v>48.84137635360887</v>
       </c>
     </row>
     <row r="147">
@@ -2297,7 +2297,7 @@
         <v>2026</v>
       </c>
       <c r="D149">
-        <v>66.38551413736946</v>
+        <v>66.90213817855545</v>
       </c>
     </row>
     <row r="150">
@@ -2310,7 +2310,7 @@
         <v>2027</v>
       </c>
       <c r="D150">
-        <v>66.63426608611341</v>
+        <v>67.04184015628287</v>
       </c>
     </row>
     <row r="151">
@@ -2323,7 +2323,7 @@
         <v>2028</v>
       </c>
       <c r="D151">
-        <v>67.21000615332999</v>
+        <v>67.68604012515166</v>
       </c>
     </row>
     <row r="152">
@@ -2362,7 +2362,7 @@
         <v>2026</v>
       </c>
       <c r="D154">
-        <v>35.78184776018659</v>
+        <v>33.41382714981616</v>
       </c>
     </row>
     <row r="155">
@@ -2375,7 +2375,7 @@
         <v>2027</v>
       </c>
       <c r="D155">
-        <v>33.40341337646209</v>
+        <v>30.97640387704919</v>
       </c>
     </row>
     <row r="156">
@@ -2388,7 +2388,7 @@
         <v>2028</v>
       </c>
       <c r="D156">
-        <v>30.97356208300224</v>
+        <v>28.53045522214135</v>
       </c>
     </row>
     <row r="157">
@@ -2427,7 +2427,7 @@
         <v>2026</v>
       </c>
       <c r="D159">
-        <v>74.06403087587363</v>
+        <v>74.77683687684889</v>
       </c>
     </row>
     <row r="160">
@@ -2440,7 +2440,7 @@
         <v>2027</v>
       </c>
       <c r="D160">
-        <v>74.74776630826314</v>
+        <v>75.4493305304544</v>
       </c>
     </row>
     <row r="161">
@@ -2453,7 +2453,7 @@
         <v>2028</v>
       </c>
       <c r="D161">
-        <v>75.46734992319142</v>
+        <v>76.175882362271</v>
       </c>
     </row>
     <row r="162">
@@ -2492,7 +2492,7 @@
         <v>2026</v>
       </c>
       <c r="D164">
-        <v>59.7748503540331</v>
+        <v>56.57763067911098</v>
       </c>
     </row>
     <row r="165">
@@ -2505,7 +2505,7 @@
         <v>2027</v>
       </c>
       <c r="D165">
-        <v>58.35603530879524</v>
+        <v>56.87156947507572</v>
       </c>
     </row>
     <row r="166">
@@ -2518,7 +2518,7 @@
         <v>2028</v>
       </c>
       <c r="D166">
-        <v>55.15647837980484</v>
+        <v>52.02023498522782</v>
       </c>
     </row>
     <row r="167">
@@ -2557,7 +2557,7 @@
         <v>2026</v>
       </c>
       <c r="D169">
-        <v>69.72754907782367</v>
+        <v>69.62781504062698</v>
       </c>
     </row>
     <row r="170">
@@ -2570,7 +2570,7 @@
         <v>2027</v>
       </c>
       <c r="D170">
-        <v>69.98021529546918</v>
+        <v>70.01739579935152</v>
       </c>
     </row>
     <row r="171">
@@ -2583,7 +2583,7 @@
         <v>2028</v>
       </c>
       <c r="D171">
-        <v>69.7987146794115</v>
+        <v>69.75093319825599</v>
       </c>
     </row>
     <row r="172">
@@ -2622,7 +2622,7 @@
         <v>2026</v>
       </c>
       <c r="D174">
-        <v>63.35739605360893</v>
+        <v>65.71556908485414</v>
       </c>
     </row>
     <row r="175">
@@ -2635,7 +2635,7 @@
         <v>2027</v>
       </c>
       <c r="D175">
-        <v>65.71574016368386</v>
+        <v>68.07784710504436</v>
       </c>
     </row>
     <row r="176">
@@ -2648,7 +2648,7 @@
         <v>2028</v>
       </c>
       <c r="D176">
-        <v>68.07785525370336</v>
+        <v>70.44014957121158</v>
       </c>
     </row>
     <row r="177">
@@ -2687,7 +2687,7 @@
         <v>2026</v>
       </c>
       <c r="D179">
-        <v>61.08084267578693</v>
+        <v>61.12101393044821</v>
       </c>
     </row>
     <row r="180">
@@ -2700,7 +2700,7 @@
         <v>2027</v>
       </c>
       <c r="D180">
-        <v>61.93343682902334</v>
+        <v>62.44092018684005</v>
       </c>
     </row>
     <row r="181">
@@ -2713,7 +2713,7 @@
         <v>2028</v>
       </c>
       <c r="D181">
-        <v>61.87071564804054</v>
+        <v>62.05021282683337</v>
       </c>
     </row>
     <row r="182">
@@ -2752,7 +2752,7 @@
         <v>2026</v>
       </c>
       <c r="D184">
-        <v>45.97499863793839</v>
+        <v>46.46549666514274</v>
       </c>
     </row>
     <row r="185">
@@ -2765,7 +2765,7 @@
         <v>2027</v>
       </c>
       <c r="D185">
-        <v>46.4655145710418</v>
+        <v>46.95541311089784</v>
       </c>
     </row>
     <row r="186">
@@ -2778,7 +2778,7 @@
         <v>2028</v>
       </c>
       <c r="D186">
-        <v>46.95541260622029</v>
+        <v>47.44532804262027</v>
       </c>
     </row>
     <row r="187">
@@ -2817,7 +2817,7 @@
         <v>2026</v>
       </c>
       <c r="D189">
-        <v>84.22261118477395</v>
+        <v>86.33681059951645</v>
       </c>
     </row>
     <row r="190">
@@ -2830,7 +2830,7 @@
         <v>2027</v>
       </c>
       <c r="D190">
-        <v>86.44630159689154</v>
+        <v>88.5229139319795</v>
       </c>
     </row>
     <row r="191">
@@ -2843,7 +2843,7 @@
         <v>2028</v>
       </c>
       <c r="D191">
-        <v>88.47618858702511</v>
+        <v>90.56884122957935</v>
       </c>
     </row>
     <row r="192">
@@ -2882,7 +2882,7 @@
         <v>2026</v>
       </c>
       <c r="D194">
-        <v>82.94068376329622</v>
+        <v>83.66279824122154</v>
       </c>
     </row>
     <row r="195">
@@ -2895,7 +2895,7 @@
         <v>2027</v>
       </c>
       <c r="D195">
-        <v>84.71723861432282</v>
+        <v>86.39335145519709</v>
       </c>
     </row>
     <row r="196">
@@ -2908,7 +2908,7 @@
         <v>2028</v>
       </c>
       <c r="D196">
-        <v>85.43061748631135</v>
+        <v>86.23570276251544</v>
       </c>
     </row>
     <row r="197">
@@ -2947,7 +2947,7 @@
         <v>2026</v>
       </c>
       <c r="D199">
-        <v>45.6216289979698</v>
+        <v>43.29933837003192</v>
       </c>
     </row>
     <row r="200">
@@ -2960,7 +2960,7 @@
         <v>2027</v>
       </c>
       <c r="D200">
-        <v>43.4041829983648</v>
+        <v>41.43708905984168</v>
       </c>
     </row>
     <row r="201">
@@ -2973,7 +2973,7 @@
         <v>2028</v>
       </c>
       <c r="D201">
-        <v>41.51263431469625</v>
+        <v>39.80147551421516</v>
       </c>
     </row>
     <row r="202">
@@ -3012,7 +3012,7 @@
         <v>2026</v>
       </c>
       <c r="D204">
-        <v>27.74796752078839</v>
+        <v>27.51245542999057</v>
       </c>
     </row>
     <row r="205">
@@ -3025,7 +3025,7 @@
         <v>2027</v>
       </c>
       <c r="D205">
-        <v>27.51330783041141</v>
+        <v>27.28767336009583</v>
       </c>
     </row>
     <row r="206">
@@ -3038,7 +3038,7 @@
         <v>2028</v>
       </c>
       <c r="D206">
-        <v>27.28776226288696</v>
+        <v>27.06315799857448</v>
       </c>
     </row>
     <row r="207">
@@ -3077,7 +3077,7 @@
         <v>2026</v>
       </c>
       <c r="D209">
-        <v>28.84930991624451</v>
+        <v>30.68830061490024</v>
       </c>
     </row>
     <row r="210">
@@ -3090,7 +3090,7 @@
         <v>2027</v>
       </c>
       <c r="D210">
-        <v>30.372933513364</v>
+        <v>32.14537299944218</v>
       </c>
     </row>
     <row r="211">
@@ -3103,7 +3103,7 @@
         <v>2028</v>
       </c>
       <c r="D211">
-        <v>32.3216569541288</v>
+        <v>34.13129724804397</v>
       </c>
     </row>
     <row r="212">
@@ -3142,7 +3142,7 @@
         <v>2026</v>
       </c>
       <c r="D214">
-        <v>17.39772028191557</v>
+        <v>16.58418897495597</v>
       </c>
     </row>
     <row r="215">
@@ -3155,7 +3155,7 @@
         <v>2027</v>
       </c>
       <c r="D215">
-        <v>16.66601123568258</v>
+        <v>16.16593062520219</v>
       </c>
     </row>
     <row r="216">
@@ -3168,7 +3168,7 @@
         <v>2028</v>
       </c>
       <c r="D216">
-        <v>16.21062092150841</v>
+        <v>15.88174316436708</v>
       </c>
     </row>
     <row r="217">
@@ -3207,7 +3207,7 @@
         <v>2026</v>
       </c>
       <c r="D219">
-        <v>59.81467663714482</v>
+        <v>61.02792067001208</v>
       </c>
     </row>
     <row r="220">
@@ -3220,7 +3220,7 @@
         <v>2027</v>
       </c>
       <c r="D220">
-        <v>61.5352609706955</v>
+        <v>62.72313830022088</v>
       </c>
     </row>
     <row r="221">
@@ -3233,7 +3233,7 @@
         <v>2028</v>
       </c>
       <c r="D221">
-        <v>62.47565515254845</v>
+        <v>63.67590648741239</v>
       </c>
     </row>
     <row r="222">
@@ -3272,7 +3272,7 @@
         <v>2026</v>
       </c>
       <c r="D224">
-        <v>54.69800688743076</v>
+        <v>55.1276500253874</v>
       </c>
     </row>
     <row r="225">
@@ -3285,7 +3285,7 @@
         <v>2027</v>
       </c>
       <c r="D225">
-        <v>55.12799609587204</v>
+        <v>55.55277663312852</v>
       </c>
     </row>
     <row r="226">
@@ -3298,7 +3298,7 @@
         <v>2028</v>
       </c>
       <c r="D226">
-        <v>55.55275507230942</v>
+        <v>55.97783855841231</v>
       </c>
     </row>
     <row r="227">
@@ -3337,7 +3337,7 @@
         <v>2026</v>
       </c>
       <c r="D229">
-        <v>78.17411015144329</v>
+        <v>78.25741154549421</v>
       </c>
     </row>
     <row r="230">
@@ -3350,7 +3350,7 @@
         <v>2027</v>
       </c>
       <c r="D230">
-        <v>78.26145931280647</v>
+        <v>78.33346576059219</v>
       </c>
     </row>
     <row r="231">
@@ -3363,7 +3363,7 @@
         <v>2028</v>
       </c>
       <c r="D231">
-        <v>78.33262078824173</v>
+        <v>78.40698505863875</v>
       </c>
     </row>
     <row r="232">
@@ -3402,7 +3402,7 @@
         <v>2026</v>
       </c>
       <c r="D234">
-        <v>79.80954579310372</v>
+        <v>80.06895027185953</v>
       </c>
     </row>
     <row r="235">
@@ -3415,7 +3415,7 @@
         <v>2027</v>
       </c>
       <c r="D235">
-        <v>80.41729070195107</v>
+        <v>80.77729617756354</v>
       </c>
     </row>
     <row r="236">
@@ -3428,7 +3428,7 @@
         <v>2028</v>
       </c>
       <c r="D236">
-        <v>80.57373108049883</v>
+        <v>80.87494679207343</v>
       </c>
     </row>
     <row r="237">
@@ -3467,7 +3467,7 @@
         <v>2026</v>
       </c>
       <c r="D239">
-        <v>68.06389829232903</v>
+        <v>66.50514719101754</v>
       </c>
     </row>
     <row r="240">
@@ -3480,7 +3480,7 @@
         <v>2027</v>
       </c>
       <c r="D240">
-        <v>68.51176404105365</v>
+        <v>69.03107557246801</v>
       </c>
     </row>
     <row r="241">
@@ -3493,7 +3493,7 @@
         <v>2028</v>
       </c>
       <c r="D241">
-        <v>70.03755891333468</v>
+        <v>74.57645397651848</v>
       </c>
     </row>
     <row r="242">
@@ -3532,7 +3532,7 @@
         <v>2026</v>
       </c>
       <c r="D244">
-        <v>43.45747056867064</v>
+        <v>43.13258007135194</v>
       </c>
     </row>
     <row r="245">
@@ -3545,7 +3545,7 @@
         <v>2027</v>
       </c>
       <c r="D245">
-        <v>43.12073709775159</v>
+        <v>42.81656002383973</v>
       </c>
     </row>
     <row r="246">
@@ -3558,7 +3558,7 @@
         <v>2028</v>
       </c>
       <c r="D246">
-        <v>42.81971898807232</v>
+        <v>42.51001686902528</v>
       </c>
     </row>
     <row r="247">
@@ -3597,7 +3597,7 @@
         <v>2026</v>
       </c>
       <c r="D249">
-        <v>66.88423056041701</v>
+        <v>67.99093505772025</v>
       </c>
     </row>
     <row r="250">
@@ -3610,7 +3610,7 @@
         <v>2027</v>
       </c>
       <c r="D250">
-        <v>68.12090375588964</v>
+        <v>69.23242631311115</v>
       </c>
     </row>
     <row r="251">
@@ -3623,7 +3623,7 @@
         <v>2028</v>
       </c>
       <c r="D251">
-        <v>69.16621470116182</v>
+        <v>70.27528273265403</v>
       </c>
     </row>
     <row r="252">
@@ -3662,7 +3662,7 @@
         <v>2026</v>
       </c>
       <c r="D254">
-        <v>82.76974101546881</v>
+        <v>83.15833089988567</v>
       </c>
     </row>
     <row r="255">
@@ -3675,7 +3675,7 @@
         <v>2027</v>
       </c>
       <c r="D255">
-        <v>83.15857286028618</v>
+        <v>83.54481723192728</v>
       </c>
     </row>
     <row r="256">
@@ -3688,7 +3688,7 @@
         <v>2028</v>
       </c>
       <c r="D256">
-        <v>83.54479654056492</v>
+        <v>83.9312414898818</v>
       </c>
     </row>
     <row r="257">
@@ -3727,7 +3727,7 @@
         <v>2026</v>
       </c>
       <c r="D259">
-        <v>85.95031406144371</v>
+        <v>86.91526903438563</v>
       </c>
     </row>
     <row r="260">
@@ -3740,7 +3740,7 @@
         <v>2027</v>
       </c>
       <c r="D260">
-        <v>86.93021331049702</v>
+        <v>87.88128088134707</v>
       </c>
     </row>
     <row r="261">
@@ -3753,7 +3753,7 @@
         <v>2028</v>
       </c>
       <c r="D261">
-        <v>87.87617919043045</v>
+        <v>88.83198765555865</v>
       </c>
     </row>
     <row r="262">
@@ -3792,7 +3792,7 @@
         <v>2026</v>
       </c>
       <c r="D264">
-        <v>48.77424245125684</v>
+        <v>50.17023873645014</v>
       </c>
     </row>
     <row r="265">
@@ -3805,7 +3805,7 @@
         <v>2027</v>
       </c>
       <c r="D265">
-        <v>49.90452280422568</v>
+        <v>51.15832870149231</v>
       </c>
     </row>
     <row r="266">
@@ -3818,7 +3818,7 @@
         <v>2028</v>
       </c>
       <c r="D266">
-        <v>51.33971984528495</v>
+        <v>52.69059209791244</v>
       </c>
     </row>
     <row r="267">
@@ -3857,7 +3857,7 @@
         <v>2026</v>
       </c>
       <c r="D269">
-        <v>70.60002266064961</v>
+        <v>73.97611802439647</v>
       </c>
     </row>
     <row r="270">
@@ -3870,7 +3870,7 @@
         <v>2027</v>
       </c>
       <c r="D270">
-        <v>73.96357469616635</v>
+        <v>77.25263167906257</v>
       </c>
     </row>
     <row r="271">
@@ -3883,7 +3883,7 @@
         <v>2028</v>
       </c>
       <c r="D271">
-        <v>77.25009203896964</v>
+        <v>80.52152641344988</v>
       </c>
     </row>
     <row r="272">
@@ -3922,7 +3922,7 @@
         <v>2026</v>
       </c>
       <c r="D274">
-        <v>62.66023433924653</v>
+        <v>64.27905840894248</v>
       </c>
     </row>
     <row r="275">
@@ -3935,7 +3935,7 @@
         <v>2027</v>
       </c>
       <c r="D275">
-        <v>64.16628348096516</v>
+        <v>65.90580437502518</v>
       </c>
     </row>
     <row r="276">
@@ -3948,7 +3948,7 @@
         <v>2028</v>
       </c>
       <c r="D276">
-        <v>65.94253594561695</v>
+        <v>67.64274505288317</v>
       </c>
     </row>
     <row r="277">
@@ -3987,7 +3987,7 @@
         <v>2026</v>
       </c>
       <c r="D279">
-        <v>76.11277564811307</v>
+        <v>77.47820492962924</v>
       </c>
     </row>
     <row r="280">
@@ -4000,7 +4000,7 @@
         <v>2027</v>
       </c>
       <c r="D280">
-        <v>77.46412154096248</v>
+        <v>78.76913211172982</v>
       </c>
     </row>
     <row r="281">
@@ -4013,7 +4013,7 @@
         <v>2028</v>
       </c>
       <c r="D281">
-        <v>78.76298234595345</v>
+        <v>80.04160999650128</v>
       </c>
     </row>
     <row r="282">
@@ -4052,7 +4052,7 @@
         <v>2026</v>
       </c>
       <c r="D284">
-        <v>58.06108327332807</v>
+        <v>60.9903113095752</v>
       </c>
     </row>
     <row r="285">
@@ -4065,7 +4065,7 @@
         <v>2027</v>
       </c>
       <c r="D285">
-        <v>60.98679518374874</v>
+        <v>63.92858951335054</v>
       </c>
     </row>
     <row r="286">
@@ -4078,7 +4078,7 @@
         <v>2028</v>
       </c>
       <c r="D286">
-        <v>63.92922033267018</v>
+        <v>66.86876017508479</v>
       </c>
     </row>
     <row r="287">
@@ -4117,7 +4117,7 @@
         <v>2026</v>
       </c>
       <c r="D289">
-        <v>26.73242473481794</v>
+        <v>28.07356669676252</v>
       </c>
     </row>
     <row r="290">
@@ -4130,7 +4130,7 @@
         <v>2027</v>
       </c>
       <c r="D290">
-        <v>28.07356667833432</v>
+        <v>29.41470838195204</v>
       </c>
     </row>
     <row r="291">
@@ -4143,7 +4143,7 @@
         <v>2028</v>
       </c>
       <c r="D291">
-        <v>29.41470838041866</v>
+        <v>30.75585006254142</v>
       </c>
     </row>
     <row r="292">
@@ -4232,7 +4232,7 @@
         <v>2026</v>
       </c>
       <c r="D299">
-        <v>37.06339336541568</v>
+        <v>36.68208770132738</v>
       </c>
     </row>
     <row r="300">
@@ -4245,7 +4245,7 @@
         <v>2027</v>
       </c>
       <c r="D300">
-        <v>36.8984972298326</v>
+        <v>36.69881875109975</v>
       </c>
     </row>
     <row r="301">
@@ -4258,7 +4258,7 @@
         <v>2028</v>
       </c>
       <c r="D301">
-        <v>36.51237528173392</v>
+        <v>36.15621939277463</v>
       </c>
     </row>
     <row r="302">
@@ -4297,7 +4297,7 @@
         <v>2026</v>
       </c>
       <c r="D304">
-        <v>37.69250758951579</v>
+        <v>38.9589057335603</v>
       </c>
     </row>
     <row r="305">
@@ -4310,7 +4310,7 @@
         <v>2027</v>
       </c>
       <c r="D305">
-        <v>38.90653015958564</v>
+        <v>40.19620749813178</v>
       </c>
     </row>
     <row r="306">
@@ -4323,7 +4323,7 @@
         <v>2028</v>
       </c>
       <c r="D306">
-        <v>40.21763367490098</v>
+        <v>41.49778779301086</v>
       </c>
     </row>
     <row r="307">
@@ -4362,7 +4362,7 @@
         <v>2026</v>
       </c>
       <c r="D309">
-        <v>43.36041131471481</v>
+        <v>42.41139193801099</v>
       </c>
     </row>
     <row r="310">
@@ -4375,7 +4375,7 @@
         <v>2027</v>
       </c>
       <c r="D310">
-        <v>42.41141750465261</v>
+        <v>41.46179444503022</v>
       </c>
     </row>
     <row r="311">
@@ -4388,7 +4388,7 @@
         <v>2028</v>
       </c>
       <c r="D311">
-        <v>41.46179344680635</v>
+        <v>40.51219395737785</v>
       </c>
     </row>
     <row r="312">
@@ -4427,7 +4427,7 @@
         <v>2026</v>
       </c>
       <c r="D314">
-        <v>44.15958712228627</v>
+        <v>44.00242540313316</v>
       </c>
     </row>
     <row r="315">
@@ -4440,7 +4440,7 @@
         <v>2027</v>
       </c>
       <c r="D315">
-        <v>44.00190918610239</v>
+        <v>43.8515809929041</v>
       </c>
     </row>
     <row r="316">
@@ -4453,7 +4453,7 @@
         <v>2028</v>
       </c>
       <c r="D316">
-        <v>43.85161487052645</v>
+        <v>43.70083821554211</v>
       </c>
     </row>
     <row r="317">
@@ -4492,7 +4492,7 @@
         <v>2026</v>
       </c>
       <c r="D319">
-        <v>39.43499507112508</v>
+        <v>39.65956540592845</v>
       </c>
     </row>
     <row r="320">
@@ -4505,7 +4505,7 @@
         <v>2027</v>
       </c>
       <c r="D320">
-        <v>40.12151303130437</v>
+        <v>40.58862993929064</v>
       </c>
     </row>
     <row r="321">
@@ -4518,7 +4518,7 @@
         <v>2028</v>
       </c>
       <c r="D321">
-        <v>40.27543404471306</v>
+        <v>40.57810678892011</v>
       </c>
     </row>
     <row r="322">
@@ -4557,7 +4557,7 @@
         <v>2026</v>
       </c>
       <c r="D324">
-        <v>64.02320859159086</v>
+        <v>64.74481385661153</v>
       </c>
     </row>
     <row r="325">
@@ -4570,7 +4570,7 @@
         <v>2027</v>
       </c>
       <c r="D325">
-        <v>64.69159758300587</v>
+        <v>65.1916625289814</v>
       </c>
     </row>
     <row r="326">
@@ -4583,7 +4583,7 @@
         <v>2028</v>
       </c>
       <c r="D326">
-        <v>65.16705974385792</v>
+        <v>65.56470284598083</v>
       </c>
     </row>
     <row r="327">
@@ -4622,7 +4622,7 @@
         <v>2026</v>
       </c>
       <c r="D329">
-        <v>72.45550905188307</v>
+        <v>72.75072941196289</v>
       </c>
     </row>
     <row r="330">
@@ -4635,7 +4635,7 @@
         <v>2027</v>
       </c>
       <c r="D330">
-        <v>72.7844776858073</v>
+        <v>73.23781006403445</v>
       </c>
     </row>
     <row r="331">
@@ -4648,7 +4648,7 @@
         <v>2028</v>
       </c>
       <c r="D331">
-        <v>73.25037906557152</v>
+        <v>73.76259772071725</v>
       </c>
     </row>
     <row r="332">
@@ -4687,7 +4687,7 @@
         <v>2026</v>
       </c>
       <c r="D334">
-        <v>58.48749605067876</v>
+        <v>59.00563837969728</v>
       </c>
     </row>
     <row r="335">
@@ -4700,7 +4700,7 @@
         <v>2027</v>
       </c>
       <c r="D335">
-        <v>59.00446244605828</v>
+        <v>59.52882068818639</v>
       </c>
     </row>
     <row r="336">
@@ -4713,7 +4713,7 @@
         <v>2028</v>
       </c>
       <c r="D336">
-        <v>59.52898208587177</v>
+        <v>60.05248718973161</v>
       </c>
     </row>
     <row r="337">
@@ -4752,7 +4752,7 @@
         <v>2026</v>
       </c>
       <c r="D339">
-        <v>79.98803457898596</v>
+        <v>81.36736323469424</v>
       </c>
     </row>
     <row r="340">
@@ -4765,7 +4765,7 @@
         <v>2027</v>
       </c>
       <c r="D340">
-        <v>81.43660582034039</v>
+        <v>82.81837158481387</v>
       </c>
     </row>
     <row r="341">
@@ -4778,7 +4778,7 @@
         <v>2028</v>
       </c>
       <c r="D341">
-        <v>82.7831301004597</v>
+        <v>84.16365548187098</v>
       </c>
     </row>
     <row r="342">
@@ -4817,7 +4817,7 @@
         <v>2026</v>
       </c>
       <c r="D344">
-        <v>46.25408363266135</v>
+        <v>45.96618529743365</v>
       </c>
     </row>
     <row r="345">
@@ -4830,7 +4830,7 @@
         <v>2027</v>
       </c>
       <c r="D345">
-        <v>45.96615182955345</v>
+        <v>45.67873649371989</v>
       </c>
     </row>
     <row r="346">
@@ -4843,7 +4843,7 @@
         <v>2028</v>
       </c>
       <c r="D346">
-        <v>45.67873853050367</v>
+        <v>45.39129380035749</v>
       </c>
     </row>
     <row r="347">
@@ -4882,7 +4882,7 @@
         <v>2026</v>
       </c>
       <c r="D349">
-        <v>61.17141846451361</v>
+        <v>62.67268300898333</v>
       </c>
     </row>
     <row r="350">
@@ -4895,7 +4895,7 @@
         <v>2027</v>
       </c>
       <c r="D350">
-        <v>63.01223672506651</v>
+        <v>64.62126423280019</v>
       </c>
     </row>
     <row r="351">
@@ -4908,7 +4908,7 @@
         <v>2028</v>
       </c>
       <c r="D351">
-        <v>64.41946526145915</v>
+        <v>65.96444854259393</v>
       </c>
     </row>
     <row r="352">
@@ -4947,7 +4947,7 @@
         <v>2026</v>
       </c>
       <c r="D354">
-        <v>54.80555881159403</v>
+        <v>55.24228267153052</v>
       </c>
     </row>
     <row r="355">
@@ -4960,7 +4960,7 @@
         <v>2027</v>
       </c>
       <c r="D355">
-        <v>55.23737891187447</v>
+        <v>55.68025929839773</v>
       </c>
     </row>
     <row r="356">
@@ -4973,7 +4973,7 @@
         <v>2028</v>
       </c>
       <c r="D356">
-        <v>55.68176561195487</v>
+        <v>56.12275486593636</v>
       </c>
     </row>
     <row r="357">
@@ -5012,7 +5012,7 @@
         <v>2026</v>
       </c>
       <c r="D359">
-        <v>26.54031690438106</v>
+        <v>24.40334489220727</v>
       </c>
     </row>
     <row r="360">
@@ -5025,7 +5025,7 @@
         <v>2027</v>
       </c>
       <c r="D360">
-        <v>24.40327715866934</v>
+        <v>22.26593052992457</v>
       </c>
     </row>
     <row r="361">
@@ -5038,7 +5038,7 @@
         <v>2028</v>
       </c>
       <c r="D361">
-        <v>22.26591134597372</v>
+        <v>20.12845861578933</v>
       </c>
     </row>
     <row r="362">
@@ -5077,7 +5077,7 @@
         <v>2026</v>
       </c>
       <c r="D364">
-        <v>37.13959691343669</v>
+        <v>38.50467196770298</v>
       </c>
     </row>
     <row r="365">
@@ -5090,7 +5090,7 @@
         <v>2027</v>
       </c>
       <c r="D365">
-        <v>38.42259046591101</v>
+        <v>39.8362916239784</v>
       </c>
     </row>
     <row r="366">
@@ -5103,7 +5103,7 @@
         <v>2028</v>
       </c>
       <c r="D366">
-        <v>39.86795383178228</v>
+        <v>41.26289790366544</v>
       </c>
     </row>
     <row r="367">
@@ -5142,7 +5142,7 @@
         <v>2026</v>
       </c>
       <c r="D369">
-        <v>23.76497067659048</v>
+        <v>23.02360970734711</v>
       </c>
     </row>
     <row r="370">
@@ -5155,7 +5155,7 @@
         <v>2027</v>
       </c>
       <c r="D370">
-        <v>23.0268603231486</v>
+        <v>22.27412397480792</v>
       </c>
     </row>
     <row r="371">
@@ -5168,7 +5168,7 @@
         <v>2028</v>
       </c>
       <c r="D371">
-        <v>22.27353289502965</v>
+        <v>21.52286500293392</v>
       </c>
     </row>
     <row r="372">
@@ -5207,7 +5207,7 @@
         <v>2026</v>
       </c>
       <c r="D374">
-        <v>58.77354873594508</v>
+        <v>61.40657394223796</v>
       </c>
     </row>
     <row r="375">
@@ -5220,7 +5220,7 @@
         <v>2027</v>
       </c>
       <c r="D375">
-        <v>61.42108386044945</v>
+        <v>64.03304788638538</v>
       </c>
     </row>
     <row r="376">
@@ -5233,7 +5233,7 @@
         <v>2028</v>
       </c>
       <c r="D376">
-        <v>64.02884394365336</v>
+        <v>66.64691000233672</v>
       </c>
     </row>
     <row r="377">
@@ -5272,7 +5272,7 @@
         <v>2026</v>
       </c>
       <c r="D379">
-        <v>51.70495668311648</v>
+        <v>51.42157559164655</v>
       </c>
     </row>
     <row r="380">
@@ -5285,7 +5285,7 @@
         <v>2027</v>
       </c>
       <c r="D380">
-        <v>51.42176489403769</v>
+        <v>51.13715023327659</v>
       </c>
     </row>
     <row r="381">
@@ -5298,7 +5298,7 @@
         <v>2028</v>
       </c>
       <c r="D381">
-        <v>51.13712800528281</v>
+        <v>50.85265819092528</v>
       </c>
     </row>
     <row r="382">
@@ -5337,7 +5337,7 @@
         <v>2026</v>
       </c>
       <c r="D384">
-        <v>38.61255499601022</v>
+        <v>39.64259276169221</v>
       </c>
     </row>
     <row r="385">
@@ -5350,7 +5350,7 @@
         <v>2027</v>
       </c>
       <c r="D385">
-        <v>39.5946870522044</v>
+        <v>40.70240354588205</v>
       </c>
     </row>
     <row r="386">
@@ -5363,7 +5363,7 @@
         <v>2028</v>
       </c>
       <c r="D386">
-        <v>40.71563171498327</v>
+        <v>41.80189883737553</v>
       </c>
     </row>
     <row r="387">
@@ -5402,7 +5402,7 @@
         <v>2026</v>
       </c>
       <c r="D389">
-        <v>21.80548168872521</v>
+        <v>22.05236391707201</v>
       </c>
     </row>
     <row r="390">
@@ -5415,7 +5415,7 @@
         <v>2027</v>
       </c>
       <c r="D390">
-        <v>22.05236437634818</v>
+        <v>22.29917543689634</v>
       </c>
     </row>
     <row r="391">
@@ -5428,7 +5428,7 @@
         <v>2028</v>
       </c>
       <c r="D391">
-        <v>22.2991754339702</v>
+        <v>22.54598694794225</v>
       </c>
     </row>
     <row r="392">
@@ -5467,7 +5467,7 @@
         <v>2026</v>
       </c>
       <c r="D394">
-        <v>14.09395337660242</v>
+        <v>15.21523427774155</v>
       </c>
     </row>
     <row r="395">
@@ -5480,7 +5480,7 @@
         <v>2027</v>
       </c>
       <c r="D395">
-        <v>15.2152319692927</v>
+        <v>16.33651527902759</v>
       </c>
     </row>
     <row r="396">
@@ -5493,7 +5493,7 @@
         <v>2028</v>
       </c>
       <c r="D396">
-        <v>16.33651603754173</v>
+        <v>17.45779855585604</v>
       </c>
     </row>
     <row r="397">
@@ -5532,7 +5532,7 @@
         <v>2026</v>
       </c>
       <c r="D399">
-        <v>15.90648895346198</v>
+        <v>18.14867510533582</v>
       </c>
     </row>
     <row r="400">
@@ -5545,7 +5545,7 @@
         <v>2027</v>
       </c>
       <c r="D400">
-        <v>18.2156927697539</v>
+        <v>20.4466308011856</v>
       </c>
     </row>
     <row r="401">
@@ -5558,7 +5558,7 @@
         <v>2028</v>
       </c>
       <c r="D401">
-        <v>20.41571628637771</v>
+        <v>22.65184295261172</v>
       </c>
     </row>
     <row r="402">
@@ -5597,7 +5597,7 @@
         <v>2026</v>
       </c>
       <c r="D404">
-        <v>4.374984583780038</v>
+        <v>3.573227120777569</v>
       </c>
     </row>
     <row r="405">
@@ -5610,7 +5610,7 @@
         <v>2027</v>
       </c>
       <c r="D405">
-        <v>3.568253276587598</v>
+        <v>2.740758239299785</v>
       </c>
     </row>
     <row r="406">
@@ -5623,7 +5623,7 @@
         <v>2028</v>
       </c>
       <c r="D406">
-        <v>2.739191468889011</v>
+        <v>1.903589046589678</v>
       </c>
     </row>
     <row r="407">
@@ -5662,7 +5662,7 @@
         <v>2026</v>
       </c>
       <c r="D409">
-        <v>6.93350991662079</v>
+        <v>6.427062328809132</v>
       </c>
     </row>
     <row r="410">
@@ -5675,7 +5675,7 @@
         <v>2027</v>
       </c>
       <c r="D410">
-        <v>6.42802287080313</v>
+        <v>5.930525922538433</v>
       </c>
     </row>
     <row r="411">
@@ -5688,7 +5688,7 @@
         <v>2028</v>
       </c>
       <c r="D411">
-        <v>5.930657174210675</v>
+        <v>5.43438327128446</v>
       </c>
     </row>
     <row r="412">
@@ -5727,7 +5727,7 @@
         <v>2026</v>
       </c>
       <c r="D414">
-        <v>14.95541167408018</v>
+        <v>15.70924014557959</v>
       </c>
     </row>
     <row r="415">
@@ -5740,7 +5740,7 @@
         <v>2027</v>
       </c>
       <c r="D415">
-        <v>15.73041599601302</v>
+        <v>16.58266487313056</v>
       </c>
     </row>
     <row r="416">
@@ -5753,7 +5753,7 @@
         <v>2028</v>
       </c>
       <c r="D416">
-        <v>16.59066250110445</v>
+        <v>17.48008248460321</v>
       </c>
     </row>
     <row r="417">
@@ -5792,7 +5792,7 @@
         <v>2026</v>
       </c>
       <c r="D419">
-        <v>17.32977594751044</v>
+        <v>18.43719908699639</v>
       </c>
     </row>
     <row r="420">
@@ -5805,7 +5805,7 @@
         <v>2027</v>
       </c>
       <c r="D420">
-        <v>18.43719908734376</v>
+        <v>19.54462243049838</v>
       </c>
     </row>
     <row r="421">
@@ -5818,7 +5818,7 @@
         <v>2028</v>
       </c>
       <c r="D421">
-        <v>19.54462243049898</v>
+        <v>20.65204577400215</v>
       </c>
     </row>
     <row r="422">
@@ -5857,7 +5857,7 @@
         <v>2026</v>
       </c>
       <c r="D424">
-        <v>30.04183634368915</v>
+        <v>31.72205140760116</v>
       </c>
     </row>
     <row r="425">
@@ -5870,7 +5870,7 @@
         <v>2027</v>
       </c>
       <c r="D425">
-        <v>31.71663373295134</v>
+        <v>33.35403914007435</v>
       </c>
     </row>
     <row r="426">
@@ -5883,7 +5883,7 @@
         <v>2028</v>
       </c>
       <c r="D426">
-        <v>33.35312117809437</v>
+        <v>34.9832729866076</v>
       </c>
     </row>
     <row r="427">
@@ -5922,7 +5922,7 @@
         <v>2026</v>
       </c>
       <c r="D429">
-        <v>8.75756051583088</v>
+        <v>8.849329893756471</v>
       </c>
     </row>
     <row r="430">
@@ -5935,7 +5935,7 @@
         <v>2027</v>
       </c>
       <c r="D430">
-        <v>8.793478441751263</v>
+        <v>8.918485424633122</v>
       </c>
     </row>
     <row r="431">
@@ -5948,7 +5948,7 @@
         <v>2028</v>
       </c>
       <c r="D431">
-        <v>8.940007252542578</v>
+        <v>9.052206439238141</v>
       </c>
     </row>
     <row r="432">
@@ -5987,7 +5987,7 @@
         <v>2026</v>
       </c>
       <c r="D434">
-        <v>20.91089547570735</v>
+        <v>20.18619518143015</v>
       </c>
     </row>
     <row r="435">
@@ -6000,7 +6000,7 @@
         <v>2027</v>
       </c>
       <c r="D435">
-        <v>20.19448005722221</v>
+        <v>19.4496325716008</v>
       </c>
     </row>
     <row r="436">
@@ -6013,7 +6013,7 @@
         <v>2028</v>
       </c>
       <c r="D436">
-        <v>19.44776315760781</v>
+        <v>18.70746171979249</v>
       </c>
     </row>
     <row r="437">
@@ -6052,7 +6052,7 @@
         <v>2026</v>
       </c>
       <c r="D439">
-        <v>26.26203504899748</v>
+        <v>27.35153543236051</v>
       </c>
     </row>
     <row r="440">
@@ -6065,7 +6065,7 @@
         <v>2027</v>
       </c>
       <c r="D440">
-        <v>27.35163289982806</v>
+        <v>28.43998829783295</v>
       </c>
     </row>
     <row r="441">
@@ -6078,7 +6078,7 @@
         <v>2028</v>
       </c>
       <c r="D441">
-        <v>28.43998120792821</v>
+        <v>29.52841989359118</v>
       </c>
     </row>
     <row r="442">
@@ -6117,7 +6117,7 @@
         <v>2026</v>
       </c>
       <c r="D444">
-        <v>33.35021902746779</v>
+        <v>35.77482705870895</v>
       </c>
     </row>
     <row r="445">
@@ -6130,7 +6130,7 @@
         <v>2027</v>
       </c>
       <c r="D445">
-        <v>35.75977970082084</v>
+        <v>38.10974476814441</v>
       </c>
     </row>
     <row r="446">
@@ -6143,7 +6143,7 @@
         <v>2028</v>
       </c>
       <c r="D446">
-        <v>38.10466212205036</v>
+        <v>40.42941453929771</v>
       </c>
     </row>
     <row r="447">
@@ -6182,7 +6182,7 @@
         <v>2026</v>
       </c>
       <c r="D449">
-        <v>36.3354812042283</v>
+        <v>37.61817873226641</v>
       </c>
     </row>
     <row r="450">
@@ -6195,7 +6195,7 @@
         <v>2027</v>
       </c>
       <c r="D450">
-        <v>37.67662951291745</v>
+        <v>38.99533637145954</v>
       </c>
     </row>
     <row r="451">
@@ -6208,7 +6208,7 @@
         <v>2028</v>
       </c>
       <c r="D451">
-        <v>38.9531012430052</v>
+        <v>40.24578862528965</v>
       </c>
     </row>
     <row r="452">
@@ -6247,7 +6247,7 @@
         <v>2026</v>
       </c>
       <c r="D454">
-        <v>26.64332562522701</v>
+        <v>25.94817200020759</v>
       </c>
     </row>
     <row r="455">
@@ -6260,7 +6260,7 @@
         <v>2027</v>
       </c>
       <c r="D455">
-        <v>25.95077180453795</v>
+        <v>25.24808114597762</v>
       </c>
     </row>
     <row r="456">
@@ -6273,7 +6273,7 @@
         <v>2028</v>
       </c>
       <c r="D456">
-        <v>25.24755047372907</v>
+        <v>24.546398275002</v>
       </c>
     </row>
     <row r="457">
@@ -6312,7 +6312,7 @@
         <v>2026</v>
       </c>
       <c r="D459">
-        <v>31.19872185696385</v>
+        <v>30.95926519465693</v>
       </c>
     </row>
     <row r="460">
@@ -6325,7 +6325,7 @@
         <v>2027</v>
       </c>
       <c r="D460">
-        <v>30.95904830816907</v>
+        <v>30.71779710464071</v>
       </c>
     </row>
     <row r="461">
@@ -6338,7 +6338,7 @@
         <v>2028</v>
       </c>
       <c r="D461">
-        <v>30.71776253611755</v>
+        <v>30.47622530905501</v>
       </c>
     </row>
     <row r="462">
@@ -6377,7 +6377,7 @@
         <v>2026</v>
       </c>
       <c r="D464">
-        <v>8.737253104125617</v>
+        <v>6.966008611264751</v>
       </c>
     </row>
     <row r="465">
@@ -6390,7 +6390,7 @@
         <v>2027</v>
       </c>
       <c r="D465">
-        <v>6.823158823460997</v>
+        <v>5.052703792814945</v>
       </c>
     </row>
     <row r="466">
@@ -6403,7 +6403,7 @@
         <v>2028</v>
       </c>
       <c r="D466">
-        <v>5.123931865032609</v>
+        <v>3.353083191018129</v>
       </c>
     </row>
     <row r="467">
@@ -6442,7 +6442,7 @@
         <v>2026</v>
       </c>
       <c r="D469">
-        <v>43.35428094065816</v>
+        <v>44.6600518836868</v>
       </c>
     </row>
     <row r="470">
@@ -6455,7 +6455,7 @@
         <v>2027</v>
       </c>
       <c r="D470">
-        <v>44.66005225979688</v>
+        <v>45.96585997218585</v>
       </c>
     </row>
     <row r="471">
@@ -6468,7 +6468,7 @@
         <v>2028</v>
       </c>
       <c r="D471">
-        <v>45.9658599761134</v>
+        <v>47.27166807246753</v>
       </c>
     </row>
     <row r="472">
@@ -6507,7 +6507,7 @@
         <v>2026</v>
       </c>
       <c r="D474">
-        <v>7.396238091109367</v>
+        <v>6.957073158597032</v>
       </c>
     </row>
     <row r="475">
@@ -6520,7 +6520,7 @@
         <v>2027</v>
       </c>
       <c r="D475">
-        <v>6.957074698814623</v>
+        <v>6.518010747338531</v>
       </c>
     </row>
     <row r="476">
@@ -6533,7 +6533,7 @@
         <v>2028</v>
       </c>
       <c r="D476">
-        <v>6.518010771569947</v>
+        <v>6.078948408774278</v>
       </c>
     </row>
     <row r="477">
@@ -6572,7 +6572,7 @@
         <v>2026</v>
       </c>
       <c r="D479">
-        <v>29.53096292155253</v>
+        <v>30.49705999986066</v>
       </c>
     </row>
     <row r="480">
@@ -6585,7 +6585,7 @@
         <v>2027</v>
       </c>
       <c r="D480">
-        <v>30.49686681398386</v>
+        <v>31.46124918669953</v>
       </c>
     </row>
     <row r="481">
@@ -6598,7 +6598,7 @@
         <v>2028</v>
       </c>
       <c r="D481">
-        <v>31.46122109076317</v>
+        <v>32.42535408572932</v>
       </c>
     </row>
     <row r="482">
@@ -6637,7 +6637,7 @@
         <v>2026</v>
       </c>
       <c r="D484">
-        <v>8.725234665287028</v>
+        <v>8.74262023673861</v>
       </c>
     </row>
     <row r="485">
@@ -6650,7 +6650,7 @@
         <v>2027</v>
       </c>
       <c r="D485">
-        <v>8.742449643955917</v>
+        <v>8.759949222740122</v>
       </c>
     </row>
     <row r="486">
@@ -6663,7 +6663,7 @@
         <v>2028</v>
       </c>
       <c r="D486">
-        <v>8.760013155849874</v>
+        <v>8.777470008070889</v>
       </c>
     </row>
     <row r="487">
@@ -6702,7 +6702,7 @@
         <v>2026</v>
       </c>
       <c r="D489">
-        <v>9.391340409702472</v>
+        <v>9.206484171234157</v>
       </c>
     </row>
     <row r="490">
@@ -6715,7 +6715,7 @@
         <v>2027</v>
       </c>
       <c r="D490">
-        <v>9.244938801022512</v>
+        <v>9.073597891803203</v>
       </c>
     </row>
     <row r="491">
@@ -6728,7 +6728,7 @@
         <v>2028</v>
       </c>
       <c r="D491">
-        <v>9.050271391229485</v>
+        <v>8.870732110651094</v>
       </c>
     </row>
     <row r="492">
@@ -6767,7 +6767,7 @@
         <v>2026</v>
       </c>
       <c r="D494">
-        <v>7.948182632084014</v>
+        <v>8.234210465256364</v>
       </c>
     </row>
     <row r="495">
@@ -6780,7 +6780,7 @@
         <v>2027</v>
       </c>
       <c r="D495">
-        <v>8.23420993476056</v>
+        <v>8.52022459962971</v>
       </c>
     </row>
     <row r="496">
@@ -6793,7 +6793,7 @@
         <v>2028</v>
       </c>
       <c r="D496">
-        <v>8.520224576385425</v>
+        <v>8.8062386642702</v>
       </c>
     </row>
     <row r="497">
@@ -6832,7 +6832,7 @@
         <v>2026</v>
       </c>
       <c r="D499">
-        <v>20.38908923661995</v>
+        <v>20.81799391226873</v>
       </c>
     </row>
     <row r="500">
@@ -6845,7 +6845,7 @@
         <v>2027</v>
       </c>
       <c r="D500">
-        <v>21.29938686409102</v>
+        <v>21.87388748943286</v>
       </c>
     </row>
     <row r="501">
@@ -6858,7 +6858,7 @@
         <v>2028</v>
       </c>
       <c r="D501">
-        <v>21.59030694253113</v>
+        <v>22.07903942589179</v>
       </c>
     </row>
     <row r="502">
@@ -6897,7 +6897,7 @@
         <v>2026</v>
       </c>
       <c r="D504">
-        <v>30.87424207568192</v>
+        <v>34.58833242246821</v>
       </c>
     </row>
     <row r="505">
@@ -6910,7 +6910,7 @@
         <v>2027</v>
       </c>
       <c r="D505">
-        <v>34.42556462014181</v>
+        <v>37.58790080965407</v>
       </c>
     </row>
     <row r="506">
@@ -6923,7 +6923,7 @@
         <v>2028</v>
       </c>
       <c r="D506">
-        <v>37.47078681892614</v>
+        <v>40.23612722465613</v>
       </c>
     </row>
     <row r="507">
@@ -6962,7 +6962,7 @@
         <v>2026</v>
       </c>
       <c r="D509">
-        <v>7.804556938642102</v>
+        <v>7.926267032256824</v>
       </c>
     </row>
     <row r="510">
@@ -6975,7 +6975,7 @@
         <v>2027</v>
       </c>
       <c r="D510">
-        <v>7.92445853208239</v>
+        <v>8.03515285836462</v>
       </c>
     </row>
     <row r="511">
@@ -6988,7 +6988,7 @@
         <v>2028</v>
       </c>
       <c r="D511">
-        <v>8.034710801885728</v>
+        <v>8.142712515035742</v>
       </c>
     </row>
     <row r="512">
@@ -7027,7 +7027,7 @@
         <v>2026</v>
       </c>
       <c r="D514">
-        <v>35.4106750706733</v>
+        <v>36.39172129932428</v>
       </c>
     </row>
     <row r="515">
@@ -7040,7 +7040,7 @@
         <v>2027</v>
       </c>
       <c r="D515">
-        <v>36.32775736114785</v>
+        <v>37.36794897428628</v>
       </c>
     </row>
     <row r="516">
@@ -7053,7 +7053,7 @@
         <v>2028</v>
       </c>
       <c r="D516">
-        <v>37.38981947233961</v>
+        <v>38.40978814340826</v>
       </c>
     </row>
     <row r="517">
@@ -7092,7 +7092,7 @@
         <v>2026</v>
       </c>
       <c r="D519">
-        <v>50.9135076460503</v>
+        <v>53.57386790583453</v>
       </c>
     </row>
     <row r="520">
@@ -7105,7 +7105,7 @@
         <v>2027</v>
       </c>
       <c r="D520">
-        <v>53.60828138536888</v>
+        <v>56.27816054320635</v>
       </c>
     </row>
     <row r="521">
@@ -7118,7 +7118,7 @@
         <v>2028</v>
       </c>
       <c r="D521">
-        <v>56.25819213497678</v>
+        <v>58.92254795588946</v>
       </c>
     </row>
     <row r="522">
@@ -7157,7 +7157,7 @@
         <v>2026</v>
       </c>
       <c r="D524">
-        <v>38.45902141331829</v>
+        <v>38.44964857065339</v>
       </c>
     </row>
     <row r="525">
@@ -7170,7 +7170,7 @@
         <v>2027</v>
       </c>
       <c r="D525">
-        <v>38.44245308707018</v>
+        <v>38.47108161052529</v>
       </c>
     </row>
     <row r="526">
@@ -7183,7 +7183,7 @@
         <v>2028</v>
       </c>
       <c r="D526">
-        <v>38.47206982732627</v>
+        <v>38.49547930080013</v>
       </c>
     </row>
     <row r="527">
@@ -7222,7 +7222,7 @@
         <v>2026</v>
       </c>
       <c r="D529">
-        <v>36.50489518179581</v>
+        <v>36.2814693399294</v>
       </c>
     </row>
     <row r="530">
@@ -7235,7 +7235,7 @@
         <v>2027</v>
       </c>
       <c r="D530">
-        <v>36.28147912176414</v>
+        <v>36.0577507218927</v>
       </c>
     </row>
     <row r="531">
@@ -7248,7 +7248,7 @@
         <v>2028</v>
       </c>
       <c r="D531">
-        <v>36.05775042484876</v>
+        <v>35.83403121272417</v>
       </c>
     </row>
     <row r="532">
@@ -7287,7 +7287,7 @@
         <v>2026</v>
       </c>
       <c r="D534">
-        <v>48.1903649390509</v>
+        <v>49.34870357702056</v>
       </c>
     </row>
     <row r="535">
@@ -7300,7 +7300,7 @@
         <v>2027</v>
       </c>
       <c r="D535">
-        <v>49.34930264570257</v>
+        <v>50.51366628850803</v>
       </c>
     </row>
     <row r="536">
@@ -7313,7 +7313,7 @@
         <v>2028</v>
       </c>
       <c r="D536">
-        <v>50.51374063968669</v>
+        <v>51.67885205353149</v>
       </c>
     </row>
     <row r="537">
@@ -7352,7 +7352,7 @@
         <v>2026</v>
       </c>
       <c r="D539">
-        <v>12.38606628241019</v>
+        <v>12.95588869601488</v>
       </c>
     </row>
     <row r="540">
@@ -7365,7 +7365,7 @@
         <v>2027</v>
       </c>
       <c r="D540">
-        <v>12.95585996474165</v>
+        <v>13.52477396135986</v>
       </c>
     </row>
     <row r="541">
@@ -7378,7 +7378,7 @@
         <v>2028</v>
       </c>
       <c r="D541">
-        <v>13.52477299128905</v>
+        <v>14.09365631649241</v>
       </c>
     </row>
     <row r="542">
@@ -7417,7 +7417,7 @@
         <v>2026</v>
       </c>
       <c r="D544">
-        <v>19.26380713431272</v>
+        <v>20.77883568046694</v>
       </c>
     </row>
     <row r="545">
@@ -7430,7 +7430,7 @@
         <v>2027</v>
       </c>
       <c r="D545">
-        <v>20.80121749023949</v>
+        <v>22.29189590985528</v>
       </c>
     </row>
     <row r="546">
@@ -7443,7 +7443,7 @@
         <v>2028</v>
       </c>
       <c r="D546">
-        <v>22.28464777996677</v>
+        <v>23.7832117495781</v>
       </c>
     </row>
     <row r="547">
@@ -7482,7 +7482,7 @@
         <v>2026</v>
       </c>
       <c r="D549">
-        <v>13.42496965352758</v>
+        <v>14.91444876687009</v>
       </c>
     </row>
     <row r="550">
@@ -7495,7 +7495,7 @@
         <v>2027</v>
       </c>
       <c r="D550">
-        <v>14.84226879384508</v>
+        <v>16.0825653714227</v>
       </c>
     </row>
     <row r="551">
@@ -7508,7 +7508,7 @@
         <v>2028</v>
       </c>
       <c r="D551">
-        <v>16.03286283573776</v>
+        <v>17.10157436892048</v>
       </c>
     </row>
     <row r="552">
@@ -7547,7 +7547,7 @@
         <v>2026</v>
       </c>
       <c r="D554">
-        <v>4.193061493878216</v>
+        <v>4.154973729977349</v>
       </c>
     </row>
     <row r="555">
@@ -7560,7 +7560,7 @@
         <v>2027</v>
       </c>
       <c r="D555">
-        <v>3.752086580159636</v>
+        <v>3.377707709495566</v>
       </c>
     </row>
     <row r="556">
@@ -7573,7 +7573,7 @@
         <v>2028</v>
       </c>
       <c r="D556">
-        <v>3.723445443992949</v>
+        <v>3.63765489250593</v>
       </c>
     </row>
     <row r="557">
@@ -7612,7 +7612,7 @@
         <v>2026</v>
       </c>
       <c r="D559">
-        <v>9.426410309504208</v>
+        <v>7.902539124986887</v>
       </c>
     </row>
     <row r="560">
@@ -7625,7 +7625,7 @@
         <v>2027</v>
       </c>
       <c r="D560">
-        <v>8.068942625703817</v>
+        <v>6.667778582275886</v>
       </c>
     </row>
     <row r="561">
@@ -7638,7 +7638,7 @@
         <v>2028</v>
       </c>
       <c r="D561">
-        <v>6.53598351584676</v>
+        <v>5.037632840277507</v>
       </c>
     </row>
     <row r="562">
@@ -7677,7 +7677,7 @@
         <v>2026</v>
       </c>
       <c r="D564">
-        <v>18.92201739951678</v>
+        <v>18.15728886154836</v>
       </c>
     </row>
     <row r="565">
@@ -7690,7 +7690,7 @@
         <v>2027</v>
       </c>
       <c r="D565">
-        <v>17.98775834565756</v>
+        <v>17.19885155339527</v>
       </c>
     </row>
     <row r="566">
@@ -7703,7 +7703,7 @@
         <v>2028</v>
       </c>
       <c r="D566">
-        <v>17.29012550634852</v>
+        <v>16.51423610410191</v>
       </c>
     </row>
     <row r="567">
@@ -7742,7 +7742,7 @@
         <v>2026</v>
       </c>
       <c r="D569">
-        <v>22.96108213049251</v>
+        <v>23.74683167146321</v>
       </c>
     </row>
     <row r="570">
@@ -7755,7 +7755,7 @@
         <v>2027</v>
       </c>
       <c r="D570">
-        <v>23.82134694092739</v>
+        <v>24.62646038012105</v>
       </c>
     </row>
     <row r="571">
@@ -7768,7 +7768,7 @@
         <v>2028</v>
       </c>
       <c r="D571">
-        <v>24.58363883902834</v>
+        <v>25.37762446550076</v>
       </c>
     </row>
     <row r="572">
@@ -7807,7 +7807,7 @@
         <v>2026</v>
       </c>
       <c r="D574">
-        <v>32.78445289677899</v>
+        <v>33.73448396077043</v>
       </c>
     </row>
     <row r="575">
@@ -7820,7 +7820,7 @@
         <v>2027</v>
       </c>
       <c r="D575">
-        <v>33.70416393987303</v>
+        <v>34.7160390797704</v>
       </c>
     </row>
     <row r="576">
@@ -7833,7 +7833,7 @@
         <v>2028</v>
       </c>
       <c r="D576">
-        <v>34.72354457260062</v>
+        <v>35.72011067726103</v>
       </c>
     </row>
     <row r="577">
@@ -7872,7 +7872,7 @@
         <v>2026</v>
       </c>
       <c r="D579">
-        <v>10.23189337010709</v>
+        <v>8.512343455417707</v>
       </c>
     </row>
     <row r="580">
@@ -7885,7 +7885,7 @@
         <v>2027</v>
       </c>
       <c r="D580">
-        <v>8.512080744174741</v>
+        <v>6.796487138068393</v>
       </c>
     </row>
     <row r="581">
@@ -7898,7 +7898,7 @@
         <v>2028</v>
       </c>
       <c r="D581">
-        <v>6.796502537742342</v>
+        <v>5.080677019740925</v>
       </c>
     </row>
     <row r="582">
@@ -7937,7 +7937,7 @@
         <v>2026</v>
       </c>
       <c r="D584">
-        <v>19.96306166269437</v>
+        <v>20.7036984834896</v>
       </c>
     </row>
     <row r="585">
@@ -7950,7 +7950,7 @@
         <v>2027</v>
       </c>
       <c r="D585">
-        <v>20.71498983088925</v>
+        <v>21.42969045767374</v>
       </c>
     </row>
     <row r="586">
@@ -7963,7 +7963,7 @@
         <v>2028</v>
       </c>
       <c r="D586">
-        <v>21.4270627279539</v>
+        <v>22.14779924269836</v>
       </c>
     </row>
     <row r="587">
@@ -8002,7 +8002,7 @@
         <v>2026</v>
       </c>
       <c r="D589">
-        <v>18.97050170209029</v>
+        <v>20.10511178690168</v>
       </c>
     </row>
     <row r="590">
@@ -8015,7 +8015,7 @@
         <v>2027</v>
       </c>
       <c r="D590">
-        <v>20.11919423270438</v>
+        <v>21.32857495923743</v>
       </c>
     </row>
     <row r="591">
@@ -8028,7 +8028,7 @@
         <v>2028</v>
       </c>
       <c r="D591">
-        <v>21.33283012687857</v>
+        <v>22.56480363449659</v>
       </c>
     </row>
     <row r="592">
@@ -8067,7 +8067,7 @@
         <v>2026</v>
       </c>
       <c r="D594">
-        <v>11.52064673809009</v>
+        <v>12.0874168149349</v>
       </c>
     </row>
     <row r="595">
@@ -8080,7 +8080,7 @@
         <v>2027</v>
       </c>
       <c r="D595">
-        <v>12.07227708366656</v>
+        <v>12.67011559905938</v>
       </c>
     </row>
     <row r="596">
@@ -8093,7 +8093,7 @@
         <v>2028</v>
       </c>
       <c r="D596">
-        <v>12.67385185504899</v>
+        <v>13.26402315115268</v>
       </c>
     </row>
     <row r="597">
@@ -8132,7 +8132,7 @@
         <v>2026</v>
       </c>
       <c r="D599">
-        <v>4.947535972792187</v>
+        <v>4.955723539801586</v>
       </c>
     </row>
     <row r="600">
@@ -8145,7 +8145,7 @@
         <v>2027</v>
       </c>
       <c r="D600">
-        <v>4.957413183834352</v>
+        <v>4.975566044827866</v>
       </c>
     </row>
     <row r="601">
@@ -8158,7 +8158,7 @@
         <v>2028</v>
       </c>
       <c r="D601">
-        <v>4.975999524085668</v>
+        <v>4.996708987627551</v>
       </c>
     </row>
     <row r="602">
@@ -8197,7 +8197,7 @@
         <v>2026</v>
       </c>
       <c r="D604">
-        <v>6.469331781395076</v>
+        <v>6.526368919304072</v>
       </c>
     </row>
     <row r="605">
@@ -8210,7 +8210,7 @@
         <v>2027</v>
       </c>
       <c r="D605">
-        <v>6.54101123591624</v>
+        <v>6.569358029872972</v>
       </c>
     </row>
     <row r="606">
@@ -8223,7 +8223,7 @@
         <v>2028</v>
       </c>
       <c r="D606">
-        <v>6.565659926894546</v>
+        <v>6.601252831506595</v>
       </c>
     </row>
     <row r="607">
@@ -8262,7 +8262,7 @@
         <v>2026</v>
       </c>
       <c r="D609">
-        <v>27.88712859182149</v>
+        <v>29.44271895611784</v>
       </c>
     </row>
     <row r="610">
@@ -8275,7 +8275,7 @@
         <v>2027</v>
       </c>
       <c r="D610">
-        <v>29.44272769196525</v>
+        <v>30.99819743863202</v>
       </c>
     </row>
     <row r="611">
@@ -8288,7 +8288,7 @@
         <v>2028</v>
       </c>
       <c r="D611">
-        <v>30.99819688598227</v>
+        <v>32.55367426319695</v>
       </c>
     </row>
     <row r="612">
@@ -8327,7 +8327,7 @@
         <v>2026</v>
       </c>
       <c r="D614">
-        <v>25.06608546135848</v>
+        <v>26.84740368162885</v>
       </c>
     </row>
     <row r="615">
@@ -8340,7 +8340,7 @@
         <v>2027</v>
       </c>
       <c r="D615">
-        <v>26.76033461244053</v>
+        <v>28.22630313040387</v>
       </c>
     </row>
     <row r="616">
@@ -8353,7 +8353,7 @@
         <v>2028</v>
       </c>
       <c r="D616">
-        <v>28.17261756388002</v>
+        <v>29.44414587960734</v>
       </c>
     </row>
     <row r="617">
@@ -8392,7 +8392,7 @@
         <v>2026</v>
       </c>
       <c r="D619">
-        <v>30.96887618675052</v>
+        <v>31.46480643757738</v>
       </c>
     </row>
     <row r="620">
@@ -8405,7 +8405,7 @@
         <v>2027</v>
       </c>
       <c r="D620">
-        <v>31.48340609558215</v>
+        <v>31.95858525606724</v>
       </c>
     </row>
     <row r="621">
@@ -8418,7 +8418,7 @@
         <v>2028</v>
       </c>
       <c r="D621">
-        <v>31.95261554334776</v>
+        <v>32.43445493639865</v>
       </c>
     </row>
     <row r="622">
@@ -8457,7 +8457,7 @@
         <v>2026</v>
       </c>
       <c r="D624">
-        <v>7.115388895236562</v>
+        <v>7.102561514761204</v>
       </c>
     </row>
     <row r="625">
@@ -8470,7 +8470,7 @@
         <v>2027</v>
       </c>
       <c r="D625">
-        <v>7.101179306752407</v>
+        <v>7.081953454208628</v>
       </c>
     </row>
     <row r="626">
@@ -8483,7 +8483,7 @@
         <v>2028</v>
       </c>
       <c r="D626">
-        <v>7.08142773337415</v>
+        <v>7.059768231152619</v>
       </c>
     </row>
     <row r="627">
@@ -8522,7 +8522,7 @@
         <v>2026</v>
       </c>
       <c r="D629">
-        <v>17.86122476459859</v>
+        <v>19.6457328178621</v>
       </c>
     </row>
     <row r="630">
@@ -8535,7 +8535,7 @@
         <v>2027</v>
       </c>
       <c r="D630">
-        <v>19.58927210462093</v>
+        <v>21.16003203356661</v>
       </c>
     </row>
     <row r="631">
@@ -8548,7 +8548,7 @@
         <v>2028</v>
       </c>
       <c r="D631">
-        <v>21.12841528712805</v>
+        <v>22.57948100995544</v>
       </c>
     </row>
     <row r="632">
@@ -8587,7 +8587,7 @@
         <v>2026</v>
       </c>
       <c r="D634">
-        <v>6.10999930391745</v>
+        <v>6.179311441149729</v>
       </c>
     </row>
     <row r="635">
@@ -8600,7 +8600,7 @@
         <v>2027</v>
       </c>
       <c r="D635">
-        <v>6.196872647032849</v>
+        <v>6.278552925771232</v>
       </c>
     </row>
     <row r="636">
@@ -8613,7 +8613,7 @@
         <v>2028</v>
       </c>
       <c r="D636">
-        <v>6.264999603755467</v>
+        <v>6.337134444345445</v>
       </c>
     </row>
     <row r="637">
@@ -8652,7 +8652,7 @@
         <v>2026</v>
       </c>
       <c r="D639">
-        <v>11.31544838045013</v>
+        <v>12.08196558478214</v>
       </c>
     </row>
     <row r="640">
@@ -8665,7 +8665,7 @@
         <v>2027</v>
       </c>
       <c r="D640">
-        <v>12.08196574997797</v>
+        <v>12.84846479497258</v>
       </c>
     </row>
     <row r="641">
@@ -8678,7 +8678,7 @@
         <v>2028</v>
       </c>
       <c r="D641">
-        <v>12.84846479349665</v>
+        <v>13.61496400073522</v>
       </c>
     </row>
     <row r="642">
@@ -8717,7 +8717,7 @@
         <v>2026</v>
       </c>
       <c r="D644">
-        <v>74.60764232914623</v>
+        <v>80.23313919281487</v>
       </c>
     </row>
     <row r="645">
@@ -8730,7 +8730,7 @@
         <v>2027</v>
       </c>
       <c r="D645">
-        <v>80.22703303615103</v>
+        <v>85.87116889526963</v>
       </c>
     </row>
     <row r="646">
@@ -8743,7 +8743,7 @@
         <v>2028</v>
       </c>
       <c r="D646">
-        <v>85.87237743878627</v>
+        <v>91.51282422827434</v>
       </c>
     </row>
     <row r="647">
@@ -8782,7 +8782,7 @@
         <v>2026</v>
       </c>
       <c r="D649">
-        <v>44.29837861845623</v>
+        <v>46.66335410943839</v>
       </c>
     </row>
     <row r="650">
@@ -8795,7 +8795,7 @@
         <v>2027</v>
       </c>
       <c r="D650">
-        <v>46.38499819899317</v>
+        <v>48.63401626274378</v>
       </c>
     </row>
     <row r="651">
@@ -8808,7 +8808,7 @@
         <v>2028</v>
       </c>
       <c r="D651">
-        <v>48.80981034215517</v>
+        <v>51.13206065428332</v>
       </c>
     </row>
     <row r="652">
@@ -8847,7 +8847,7 @@
         <v>2026</v>
       </c>
       <c r="D654">
-        <v>12.47477554862139</v>
+        <v>13.21045685242041</v>
       </c>
     </row>
     <row r="655">
@@ -8860,7 +8860,7 @@
         <v>2027</v>
       </c>
       <c r="D655">
-        <v>12.57507114479166</v>
+        <v>13.04452712249086</v>
       </c>
     </row>
     <row r="656">
@@ -8873,7 +8873,7 @@
         <v>2028</v>
       </c>
       <c r="D656">
-        <v>13.44641510136638</v>
+        <v>14.08426132918787</v>
       </c>
     </row>
     <row r="657">
@@ -8912,7 +8912,7 @@
         <v>2026</v>
       </c>
       <c r="D659">
-        <v>52.22978922105366</v>
+        <v>55.394657626065</v>
       </c>
     </row>
     <row r="660">
@@ -8925,7 +8925,7 @@
         <v>2027</v>
       </c>
       <c r="D660">
-        <v>55.39465272851839</v>
+        <v>58.55929303864956</v>
       </c>
     </row>
     <row r="661">
@@ -8938,7 +8938,7 @@
         <v>2028</v>
       </c>
       <c r="D661">
-        <v>58.55929292877331</v>
+        <v>61.72392812160534</v>
       </c>
     </row>
     <row r="662">
@@ -8977,7 +8977,7 @@
         <v>2026</v>
       </c>
       <c r="D664">
-        <v>94.37833784105733</v>
+        <v>99.40700470319365</v>
       </c>
     </row>
     <row r="665">
@@ -8990,7 +8990,7 @@
         <v>2027</v>
       </c>
       <c r="D665">
-        <v>99.40814654982928</v>
+        <v>100</v>
       </c>
     </row>
     <row r="666">
@@ -9042,7 +9042,7 @@
         <v>2026</v>
       </c>
       <c r="D669">
-        <v>58.6367760578402</v>
+        <v>62.3999508081127</v>
       </c>
     </row>
     <row r="670">
@@ -9055,7 +9055,7 @@
         <v>2027</v>
       </c>
       <c r="D670">
-        <v>62.45706527679484</v>
+        <v>66.17224824791802</v>
       </c>
     </row>
     <row r="671">
@@ -9068,7 +9068,7 @@
         <v>2028</v>
       </c>
       <c r="D671">
-        <v>66.15213945661843</v>
+        <v>69.88421931382456</v>
       </c>
     </row>
     <row r="672">
@@ -9107,7 +9107,7 @@
         <v>2026</v>
       </c>
       <c r="D674">
-        <v>24.90157128635557</v>
+        <v>26.99380476106554</v>
       </c>
     </row>
     <row r="675">
@@ -9120,7 +9120,7 @@
         <v>2027</v>
       </c>
       <c r="D675">
-        <v>26.95453726456917</v>
+        <v>28.86107097381714</v>
       </c>
     </row>
     <row r="676">
@@ -9133,7 +9133,7 @@
         <v>2028</v>
       </c>
       <c r="D676">
-        <v>28.84668251158685</v>
+        <v>30.68517179987786</v>
       </c>
     </row>
     <row r="677">
@@ -9172,7 +9172,7 @@
         <v>2026</v>
       </c>
       <c r="D679">
-        <v>4.39674790432441</v>
+        <v>3.941429713003313</v>
       </c>
     </row>
     <row r="680">
@@ -9185,7 +9185,7 @@
         <v>2027</v>
       </c>
       <c r="D680">
-        <v>4.191861190365498</v>
+        <v>3.841891456875471</v>
       </c>
     </row>
     <row r="681">
@@ -9198,7 +9198,7 @@
         <v>2028</v>
       </c>
       <c r="D681">
-        <v>3.683323502106607</v>
+        <v>3.266649336441038</v>
       </c>
     </row>
     <row r="682">
@@ -9237,7 +9237,7 @@
         <v>2026</v>
       </c>
       <c r="D684">
-        <v>8.780851931376434</v>
+        <v>9.327235552680396</v>
       </c>
     </row>
     <row r="685">
@@ -9250,7 +9250,7 @@
         <v>2027</v>
       </c>
       <c r="D685">
-        <v>9.325584431438473</v>
+        <v>9.863509581911275</v>
       </c>
     </row>
     <row r="686">
@@ -9263,7 +9263,7 @@
         <v>2028</v>
       </c>
       <c r="D686">
-        <v>9.862980861852369</v>
+        <v>10.39819745096544</v>
       </c>
     </row>
     <row r="687">
@@ -9302,7 +9302,7 @@
         <v>2026</v>
       </c>
       <c r="D689">
-        <v>12.88234738147041</v>
+        <v>13.15218555742515</v>
       </c>
     </row>
     <row r="690">
@@ -9315,7 +9315,7 @@
         <v>2027</v>
       </c>
       <c r="D690">
-        <v>12.9221047102935</v>
+        <v>13.07732860420802</v>
       </c>
     </row>
     <row r="691">
@@ -9328,7 +9328,7 @@
         <v>2028</v>
       </c>
       <c r="D691">
-        <v>13.23052667296578</v>
+        <v>13.46206585726417</v>
       </c>
     </row>
     <row r="692">
@@ -9367,7 +9367,7 @@
         <v>2026</v>
       </c>
       <c r="D694">
-        <v>32.90126124567443</v>
+        <v>33.31813529833398</v>
       </c>
     </row>
     <row r="695">
@@ -9380,7 +9380,7 @@
         <v>2027</v>
       </c>
       <c r="D695">
-        <v>33.31921320495714</v>
+        <v>33.73157795234731</v>
       </c>
     </row>
     <row r="696">
@@ -9393,7 +9393,7 @@
         <v>2028</v>
       </c>
       <c r="D696">
-        <v>33.73140362946234</v>
+        <v>34.14449763770575</v>
       </c>
     </row>
     <row r="697">
@@ -9432,7 +9432,7 @@
         <v>2026</v>
       </c>
       <c r="D699">
-        <v>17.02676376769375</v>
+        <v>17.63252617271802</v>
       </c>
     </row>
     <row r="700">
@@ -9445,7 +9445,7 @@
         <v>2027</v>
       </c>
       <c r="D700">
-        <v>18.61163272472852</v>
+        <v>19.92743543916948</v>
       </c>
     </row>
     <row r="701">
@@ -9458,7 +9458,7 @@
         <v>2028</v>
       </c>
       <c r="D701">
-        <v>19.15939303003029</v>
+        <v>19.91821747820337</v>
       </c>
     </row>
     <row r="702">
@@ -9497,7 +9497,7 @@
         <v>2026</v>
       </c>
       <c r="D704">
-        <v>40.24563937947769</v>
+        <v>42.38526988944414</v>
       </c>
     </row>
     <row r="705">
@@ -9510,7 +9510,7 @@
         <v>2027</v>
       </c>
       <c r="D705">
-        <v>43.1549451767249</v>
+        <v>45.88168010633306</v>
       </c>
     </row>
     <row r="706">
@@ -9523,7 +9523,7 @@
         <v>2028</v>
       </c>
       <c r="D706">
-        <v>45.2595720045675</v>
+        <v>47.51176601792527</v>
       </c>
     </row>
     <row r="707">
@@ -9562,7 +9562,7 @@
         <v>2026</v>
       </c>
       <c r="D709">
-        <v>29.10513558564645</v>
+        <v>30.81107121795119</v>
       </c>
     </row>
     <row r="710">
@@ -9575,7 +9575,7 @@
         <v>2027</v>
       </c>
       <c r="D710">
-        <v>30.84676216743205</v>
+        <v>32.50185487993255</v>
       </c>
     </row>
     <row r="711">
@@ -9588,7 +9588,7 @@
         <v>2028</v>
       </c>
       <c r="D711">
-        <v>32.49143274236911</v>
+        <v>34.16137212922359</v>
       </c>
     </row>
     <row r="712">
@@ -9627,7 +9627,7 @@
         <v>2026</v>
       </c>
       <c r="D714">
-        <v>64.73706371732992</v>
+        <v>67.31547619667082</v>
       </c>
     </row>
     <row r="715">
@@ -9640,7 +9640,7 @@
         <v>2027</v>
       </c>
       <c r="D715">
-        <v>67.31536893897487</v>
+        <v>69.89637689374354</v>
       </c>
     </row>
     <row r="716">
@@ -9653,7 +9653,7 @@
         <v>2028</v>
       </c>
       <c r="D716">
-        <v>69.896380987783</v>
+        <v>72.47728987293468</v>
       </c>
     </row>
     <row r="717">
@@ -9692,7 +9692,7 @@
         <v>2026</v>
       </c>
       <c r="D719">
-        <v>72.84895405143317</v>
+        <v>76.66127371044223</v>
       </c>
     </row>
     <row r="720">
@@ -9705,7 +9705,7 @@
         <v>2027</v>
       </c>
       <c r="D720">
-        <v>75.40702248105208</v>
+        <v>78.73103525536234</v>
       </c>
     </row>
     <row r="721">
@@ -9718,7 +9718,7 @@
         <v>2028</v>
       </c>
       <c r="D721">
-        <v>79.50974508257397</v>
+        <v>83.13692628191735</v>
       </c>
     </row>
     <row r="722">
@@ -9757,7 +9757,7 @@
         <v>2026</v>
       </c>
       <c r="D724">
-        <v>35.36694828628439</v>
+        <v>38.18479417303111</v>
       </c>
     </row>
     <row r="725">
@@ -9770,7 +9770,7 @@
         <v>2027</v>
       </c>
       <c r="D725">
-        <v>38.18473012986811</v>
+        <v>41.00443628768394</v>
       </c>
     </row>
     <row r="726">
@@ -9783,7 +9783,7 @@
         <v>2028</v>
       </c>
       <c r="D726">
-        <v>41.00443835045532</v>
+        <v>43.82408459065091</v>
       </c>
     </row>
     <row r="727">
@@ -9822,7 +9822,7 @@
         <v>2026</v>
       </c>
       <c r="D729">
-        <v>75.06058091632217</v>
+        <v>77.43903226082202</v>
       </c>
     </row>
     <row r="730">
@@ -9835,7 +9835,7 @@
         <v>2027</v>
       </c>
       <c r="D730">
-        <v>77.72119791926166</v>
+        <v>80.3648947535555</v>
       </c>
     </row>
     <row r="731">
@@ -9848,7 +9848,7 @@
         <v>2028</v>
       </c>
       <c r="D731">
-        <v>80.09869203984425</v>
+        <v>82.49214910515522</v>
       </c>
     </row>
     <row r="732">
@@ -9887,7 +9887,7 @@
         <v>2026</v>
       </c>
       <c r="D734">
-        <v>69.67498237049318</v>
+        <v>73.74689054982795</v>
       </c>
     </row>
     <row r="735">
@@ -9900,7 +9900,7 @@
         <v>2027</v>
       </c>
       <c r="D735">
-        <v>71.7380201565045</v>
+        <v>73.97504927457524</v>
       </c>
     </row>
     <row r="736">
@@ -9913,7 +9913,7 @@
         <v>2028</v>
       </c>
       <c r="D736">
-        <v>75.82379682016871</v>
+        <v>79.74945063610294</v>
       </c>
     </row>
     <row r="737">
@@ -9952,7 +9952,7 @@
         <v>2026</v>
       </c>
       <c r="D739">
-        <v>61.41388495950444</v>
+        <v>60.27566918088542</v>
       </c>
     </row>
     <row r="740">
@@ -9965,7 +9965,7 @@
         <v>2027</v>
       </c>
       <c r="D740">
-        <v>60.27127118561258</v>
+        <v>59.13065670660077</v>
       </c>
     </row>
     <row r="741">
@@ -9978,7 +9978,7 @@
         <v>2028</v>
       </c>
       <c r="D741">
-        <v>59.13368023093025</v>
+        <v>57.99471480530452</v>
       </c>
     </row>
     <row r="742">
@@ -10017,7 +10017,7 @@
         <v>2026</v>
       </c>
       <c r="D744">
-        <v>60.04885478346424</v>
+        <v>61.55262641984903</v>
       </c>
     </row>
     <row r="745">
@@ -10030,7 +10030,7 @@
         <v>2027</v>
       </c>
       <c r="D745">
-        <v>61.54483699731325</v>
+        <v>63.07905210125821</v>
       </c>
     </row>
     <row r="746">
@@ -10043,7 +10043,7 @@
         <v>2028</v>
       </c>
       <c r="D746">
-        <v>63.08037048575414</v>
+        <v>64.60943293615522</v>
       </c>
     </row>
     <row r="747">
@@ -10082,7 +10082,7 @@
         <v>2026</v>
       </c>
       <c r="D749">
-        <v>43.10290485413461</v>
+        <v>44.56330520722478</v>
       </c>
     </row>
     <row r="750">
@@ -10095,7 +10095,7 @@
         <v>2027</v>
       </c>
       <c r="D750">
-        <v>44.5633299822077</v>
+        <v>46.02344454727809</v>
       </c>
     </row>
     <row r="751">
@@ -10108,7 +10108,7 @@
         <v>2028</v>
       </c>
       <c r="D751">
-        <v>46.02344271688665</v>
+        <v>47.48357839615707</v>
       </c>
     </row>
     <row r="752">
@@ -10147,7 +10147,7 @@
         <v>2026</v>
       </c>
       <c r="D754">
-        <v>45.8520410068744</v>
+        <v>49.60245884603601</v>
       </c>
     </row>
     <row r="755">
@@ -10160,7 +10160,7 @@
         <v>2027</v>
       </c>
       <c r="D755">
-        <v>49.58618569803455</v>
+        <v>53.23173602335652</v>
       </c>
     </row>
     <row r="756">
@@ -10173,7 +10173,7 @@
         <v>2028</v>
       </c>
       <c r="D756">
-        <v>53.22807436839829</v>
+        <v>56.85002823580233</v>
       </c>
     </row>
     <row r="757">
@@ -10212,7 +10212,7 @@
         <v>2026</v>
       </c>
       <c r="D759">
-        <v>24.46719913468094</v>
+        <v>25.87080606444419</v>
       </c>
     </row>
     <row r="760">
@@ -10225,7 +10225,7 @@
         <v>2027</v>
       </c>
       <c r="D760">
-        <v>25.87080499387147</v>
+        <v>27.27433989952679</v>
       </c>
     </row>
     <row r="761">
@@ -10238,7 +10238,7 @@
         <v>2028</v>
       </c>
       <c r="D761">
-        <v>27.27433988312615</v>
+        <v>28.67787368540746</v>
       </c>
     </row>
     <row r="762">
@@ -10277,7 +10277,7 @@
         <v>2026</v>
       </c>
       <c r="D764">
-        <v>13.62015590472696</v>
+        <v>14.75911396116835</v>
       </c>
     </row>
     <row r="765">
@@ -10290,7 +10290,7 @@
         <v>2027</v>
       </c>
       <c r="D765">
-        <v>14.73385501390381</v>
+        <v>15.77289901627632</v>
       </c>
     </row>
     <row r="766">
@@ -10303,7 +10303,7 @@
         <v>2028</v>
       </c>
       <c r="D766">
-        <v>15.75998274054037</v>
+        <v>16.74793524417642</v>
       </c>
     </row>
     <row r="767">
@@ -10342,7 +10342,7 @@
         <v>2026</v>
       </c>
       <c r="D769">
-        <v>19.4725511889298</v>
+        <v>20.57065714065589</v>
       </c>
     </row>
     <row r="770">
@@ -10355,7 +10355,7 @@
         <v>2027</v>
       </c>
       <c r="D770">
-        <v>20.57080837905634</v>
+        <v>21.67169812822736</v>
       </c>
     </row>
     <row r="771">
@@ -10368,7 +10368,7 @@
         <v>2028</v>
       </c>
       <c r="D771">
-        <v>21.67170734632412</v>
+        <v>22.7727667700891</v>
       </c>
     </row>
     <row r="772">
@@ -10407,7 +10407,7 @@
         <v>2026</v>
       </c>
       <c r="D774">
-        <v>9.687553189459059</v>
+        <v>10.1180397037804</v>
       </c>
     </row>
     <row r="775">
@@ -10420,7 +10420,7 @@
         <v>2027</v>
       </c>
       <c r="D775">
-        <v>10.11948809654479</v>
+        <v>10.55892431489106</v>
       </c>
     </row>
     <row r="776">
@@ -10433,7 +10433,7 @@
         <v>2028</v>
       </c>
       <c r="D776">
-        <v>10.55927089837823</v>
+        <v>11.00084867646324</v>
       </c>
     </row>
     <row r="777">
@@ -10472,7 +10472,7 @@
         <v>2026</v>
       </c>
       <c r="D779">
-        <v>36.97299825852101</v>
+        <v>38.80946638198193</v>
       </c>
     </row>
     <row r="780">
@@ -10485,7 +10485,7 @@
         <v>2027</v>
       </c>
       <c r="D780">
-        <v>38.80944599775124</v>
+        <v>40.64563489913908</v>
       </c>
     </row>
     <row r="781">
@@ -10498,7 +10498,7 @@
         <v>2028</v>
       </c>
       <c r="D781">
-        <v>40.6456331565911</v>
+        <v>42.48179818865226</v>
       </c>
     </row>
     <row r="782">
@@ -10537,7 +10537,7 @@
         <v>2026</v>
       </c>
       <c r="D784">
-        <v>23.69475503643902</v>
+        <v>24.60446269967257</v>
       </c>
     </row>
     <row r="785">
@@ -10550,7 +10550,7 @@
         <v>2027</v>
       </c>
       <c r="D785">
-        <v>24.60865741720751</v>
+        <v>25.51513875020119</v>
       </c>
     </row>
     <row r="786">
@@ -10563,7 +10563,7 @@
         <v>2028</v>
       </c>
       <c r="D786">
-        <v>25.51362394211677</v>
+        <v>26.42127037647654</v>
       </c>
     </row>
     <row r="787">
@@ -10602,7 +10602,7 @@
         <v>2026</v>
       </c>
       <c r="D789">
-        <v>17.8156514331035</v>
+        <v>19.19236146482976</v>
       </c>
     </row>
     <row r="790">
@@ -10615,7 +10615,7 @@
         <v>2027</v>
       </c>
       <c r="D790">
-        <v>19.19308504979665</v>
+        <v>20.57385102780207</v>
       </c>
     </row>
     <row r="791">
@@ -10628,7 +10628,7 @@
         <v>2028</v>
       </c>
       <c r="D791">
-        <v>20.57405172542233</v>
+        <v>21.95594268363517</v>
       </c>
     </row>
     <row r="792">
@@ -10667,7 +10667,7 @@
         <v>2026</v>
       </c>
       <c r="D794">
-        <v>20.95815832626235</v>
+        <v>22.61190848786381</v>
       </c>
     </row>
     <row r="795">
@@ -10680,7 +10680,7 @@
         <v>2027</v>
       </c>
       <c r="D795">
-        <v>22.6165852910734</v>
+        <v>24.28811800388039</v>
       </c>
     </row>
     <row r="796">
@@ -10693,7 +10693,7 @@
         <v>2028</v>
       </c>
       <c r="D796">
-        <v>24.29071292991389</v>
+        <v>25.97211229799748</v>
       </c>
     </row>
     <row r="797">
@@ -10732,7 +10732,7 @@
         <v>2026</v>
       </c>
       <c r="D799">
-        <v>4.784271088560705</v>
+        <v>4.770563136574169</v>
       </c>
     </row>
     <row r="800">
@@ -10745,7 +10745,7 @@
         <v>2027</v>
       </c>
       <c r="D800">
-        <v>4.745347119335881</v>
+        <v>4.730313842411409</v>
       </c>
     </row>
     <row r="801">
@@ -10758,7 +10758,7 @@
         <v>2028</v>
       </c>
       <c r="D801">
-        <v>4.74326212445546</v>
+        <v>4.728909394380803</v>
       </c>
     </row>
     <row r="802">
@@ -10797,7 +10797,7 @@
         <v>2026</v>
       </c>
       <c r="D804">
-        <v>69.1146159319553</v>
+        <v>73.2213008915372</v>
       </c>
     </row>
     <row r="805">
@@ -10810,7 +10810,7 @@
         <v>2027</v>
       </c>
       <c r="D805">
-        <v>73.22174694970336</v>
+        <v>77.33669188788883</v>
       </c>
     </row>
     <row r="806">
@@ -10823,7 +10823,7 @@
         <v>2028</v>
       </c>
       <c r="D806">
-        <v>77.33671889272149</v>
+        <v>81.45216389873843</v>
       </c>
     </row>
     <row r="807">
@@ -10862,7 +10862,7 @@
         <v>2026</v>
       </c>
       <c r="D809">
-        <v>35.68185760738552</v>
+        <v>36.23326436645033</v>
       </c>
     </row>
     <row r="810">
@@ -10875,7 +10875,7 @@
         <v>2027</v>
       </c>
       <c r="D810">
-        <v>36.20763264186683</v>
+        <v>36.79720977171016</v>
       </c>
     </row>
     <row r="811">
@@ -10888,7 +10888,7 @@
         <v>2028</v>
       </c>
       <c r="D811">
-        <v>36.80455582162199</v>
+        <v>37.38319332670547</v>
       </c>
     </row>
     <row r="812">
@@ -10927,7 +10927,7 @@
         <v>2026</v>
       </c>
       <c r="D814">
-        <v>40.38312659887484</v>
+        <v>43.55845215810976</v>
       </c>
     </row>
     <row r="815">
@@ -10940,7 +10940,7 @@
         <v>2027</v>
       </c>
       <c r="D815">
-        <v>43.52373031475408</v>
+        <v>46.53892641824855</v>
       </c>
     </row>
     <row r="816">
@@ -10953,7 +10953,7 @@
         <v>2028</v>
       </c>
       <c r="D816">
-        <v>46.52563208972353</v>
+        <v>49.47951769281227</v>
       </c>
     </row>
     <row r="817">
@@ -10992,7 +10992,7 @@
         <v>2026</v>
       </c>
       <c r="D819">
-        <v>45.45149851415271</v>
+        <v>49.44400563850114</v>
       </c>
     </row>
     <row r="820">
@@ -11005,7 +11005,7 @@
         <v>2027</v>
       </c>
       <c r="D820">
-        <v>49.44754336542121</v>
+        <v>53.46949099950985</v>
       </c>
     </row>
     <row r="821">
@@ -11018,7 +11018,7 @@
         <v>2028</v>
       </c>
       <c r="D821">
-        <v>53.47005060069381</v>
+        <v>57.49665516407044</v>
       </c>
     </row>
     <row r="822">
@@ -11057,7 +11057,7 @@
         <v>2026</v>
       </c>
       <c r="D824">
-        <v>47.81282915567638</v>
+        <v>51.88721677161337</v>
       </c>
     </row>
     <row r="825">
@@ -11070,7 +11070,7 @@
         <v>2027</v>
       </c>
       <c r="D825">
-        <v>51.88680835660949</v>
+        <v>55.9558719734427</v>
       </c>
     </row>
     <row r="826">
@@ -11083,7 +11083,7 @@
         <v>2028</v>
       </c>
       <c r="D826">
-        <v>55.95583496510957</v>
+        <v>60.02441615027264</v>
       </c>
     </row>
     <row r="827">
@@ -11122,7 +11122,7 @@
         <v>2026</v>
       </c>
       <c r="D829">
-        <v>59.05671571670266</v>
+        <v>63.37182171580285</v>
       </c>
     </row>
     <row r="830">
@@ -11135,7 +11135,7 @@
         <v>2027</v>
       </c>
       <c r="D830">
-        <v>63.37124070838888</v>
+        <v>67.69311621943724</v>
       </c>
     </row>
     <row r="831">
@@ -11148,7 +11148,7 @@
         <v>2028</v>
       </c>
       <c r="D831">
-        <v>67.69315877992081</v>
+        <v>72.01453840452236</v>
       </c>
     </row>
     <row r="832">
@@ -11187,7 +11187,7 @@
         <v>2026</v>
       </c>
       <c r="D834">
-        <v>47.38487997965104</v>
+        <v>51.97831936512798</v>
       </c>
     </row>
     <row r="835">
@@ -11200,7 +11200,7 @@
         <v>2027</v>
       </c>
       <c r="D835">
-        <v>51.89805138563275</v>
+        <v>56.19415813002054</v>
       </c>
     </row>
     <row r="836">
@@ -11213,7 +11213,7 @@
         <v>2028</v>
       </c>
       <c r="D836">
-        <v>56.14705941071387</v>
+        <v>60.26870073699311</v>
       </c>
     </row>
     <row r="837">
@@ -11252,7 +11252,7 @@
         <v>2026</v>
       </c>
       <c r="D839">
-        <v>10.86069360602246</v>
+        <v>12.01982276404056</v>
       </c>
     </row>
     <row r="840">
@@ -11265,7 +11265,7 @@
         <v>2027</v>
       </c>
       <c r="D840">
-        <v>10.99480443358928</v>
+        <v>11.54413111862612</v>
       </c>
     </row>
     <row r="841">
@@ -11278,7 +11278,7 @@
         <v>2028</v>
       </c>
       <c r="D841">
-        <v>12.27363926846219</v>
+        <v>13.2569639227199</v>
       </c>
     </row>
     <row r="842">
@@ -11317,7 +11317,7 @@
         <v>2026</v>
       </c>
       <c r="D844">
-        <v>6.862959524476761</v>
+        <v>6.798041672494008</v>
       </c>
     </row>
     <row r="845">
@@ -11330,7 +11330,7 @@
         <v>2027</v>
       </c>
       <c r="D845">
-        <v>6.797948908426606</v>
+        <v>6.731492263402964</v>
       </c>
     </row>
     <row r="846">
@@ -11343,7 +11343,7 @@
         <v>2028</v>
       </c>
       <c r="D846">
-        <v>6.731485904579823</v>
+        <v>6.664923777842494</v>
       </c>
     </row>
     <row r="847">
@@ -11382,7 +11382,7 @@
         <v>2026</v>
       </c>
       <c r="D849">
-        <v>23.97636500986167</v>
+        <v>24.57113700934495</v>
       </c>
     </row>
     <row r="850">
@@ -11395,7 +11395,7 @@
         <v>2027</v>
       </c>
       <c r="D850">
-        <v>24.56546918433331</v>
+        <v>25.17762304698186</v>
       </c>
     </row>
     <row r="851">
@@ -11408,7 +11408,7 @@
         <v>2028</v>
       </c>
       <c r="D851">
-        <v>25.17874167588791</v>
+        <v>25.78746497133692</v>
       </c>
     </row>
     <row r="852">
@@ -11447,7 +11447,7 @@
         <v>2026</v>
       </c>
       <c r="D854">
-        <v>6.62361141374537</v>
+        <v>6.624883140480482</v>
       </c>
     </row>
     <row r="855">
@@ -11460,7 +11460,7 @@
         <v>2027</v>
       </c>
       <c r="D855">
-        <v>6.623585870645573</v>
+        <v>6.625184527359793</v>
       </c>
     </row>
     <row r="856">
@@ -11473,7 +11473,7 @@
         <v>2028</v>
       </c>
       <c r="D856">
-        <v>6.625760576138937</v>
+        <v>6.627214060576533</v>
       </c>
     </row>
     <row r="857">
@@ -11512,7 +11512,7 @@
         <v>2026</v>
       </c>
       <c r="D859">
-        <v>34.36627085635778</v>
+        <v>36.09239383734964</v>
       </c>
     </row>
     <row r="860">
@@ -11525,7 +11525,7 @@
         <v>2027</v>
       </c>
       <c r="D860">
-        <v>36.09385997376949</v>
+        <v>37.81791744110522</v>
       </c>
     </row>
     <row r="861">
@@ -11538,7 +11538,7 @@
         <v>2028</v>
       </c>
       <c r="D861">
-        <v>37.81748733949856</v>
+        <v>39.54215074004083</v>
       </c>
     </row>
     <row r="862">
@@ -11577,7 +11577,7 @@
         <v>2026</v>
       </c>
       <c r="D864">
-        <v>33.31295725509236</v>
+        <v>34.76095856845701</v>
       </c>
     </row>
     <row r="865">
@@ -11590,7 +11590,7 @@
         <v>2027</v>
       </c>
       <c r="D865">
-        <v>34.76095848464421</v>
+        <v>36.20894696127694</v>
       </c>
     </row>
     <row r="866">
@@ -11603,7 +11603,7 @@
         <v>2028</v>
       </c>
       <c r="D866">
-        <v>36.20894696072247</v>
+        <v>37.65693535243347</v>
       </c>
     </row>
     <row r="867">
@@ -11642,7 +11642,7 @@
         <v>2026</v>
       </c>
       <c r="D869">
-        <v>28.98302741407004</v>
+        <v>31.16134074349303</v>
       </c>
     </row>
     <row r="870">
@@ -11655,7 +11655,7 @@
         <v>2027</v>
       </c>
       <c r="D870">
-        <v>31.16375937817755</v>
+        <v>33.3312316943699</v>
       </c>
     </row>
     <row r="871">
@@ -11668,7 +11668,7 @@
         <v>2028</v>
       </c>
       <c r="D871">
-        <v>33.33085857992321</v>
+        <v>35.50000330190671</v>
       </c>
     </row>
     <row r="872">
@@ -11707,7 +11707,7 @@
         <v>2026</v>
       </c>
       <c r="D874">
-        <v>18.45579997926103</v>
+        <v>19.03275494075471</v>
       </c>
     </row>
     <row r="875">
@@ -11720,7 +11720,7 @@
         <v>2027</v>
       </c>
       <c r="D875">
-        <v>19.03607360000712</v>
+        <v>19.60685760951858</v>
       </c>
     </row>
     <row r="876">
@@ -11733,7 +11733,7 @@
         <v>2028</v>
       </c>
       <c r="D876">
-        <v>19.60599773548291</v>
+        <v>20.17838065617545</v>
       </c>
     </row>
     <row r="877">
@@ -11772,7 +11772,7 @@
         <v>2026</v>
       </c>
       <c r="D879">
-        <v>11.3403974533214</v>
+        <v>11.97492343644547</v>
       </c>
     </row>
     <row r="880">
@@ -11785,7 +11785,7 @@
         <v>2027</v>
       </c>
       <c r="D880">
-        <v>11.97494740645323</v>
+        <v>12.61024361012527</v>
       </c>
     </row>
     <row r="881">
@@ -11798,7 +11798,7 @@
         <v>2028</v>
       </c>
       <c r="D881">
-        <v>12.61024440560743</v>
+        <v>13.24556617025154</v>
       </c>
     </row>
     <row r="882">
@@ -11837,7 +11837,7 @@
         <v>2026</v>
       </c>
       <c r="D884">
-        <v>7.025132749972489</v>
+        <v>6.683860962567226</v>
       </c>
     </row>
     <row r="885">
@@ -11850,7 +11850,7 @@
         <v>2027</v>
       </c>
       <c r="D885">
-        <v>6.683816446943059</v>
+        <v>6.34173637025262</v>
       </c>
     </row>
     <row r="886">
@@ -11863,7 +11863,7 @@
         <v>2028</v>
       </c>
       <c r="D886">
-        <v>6.341733615134577</v>
+        <v>5.999603512583884</v>
       </c>
     </row>
     <row r="887">
@@ -11902,7 +11902,7 @@
         <v>2026</v>
       </c>
       <c r="D889">
-        <v>10.33264473723345</v>
+        <v>10.44610820170821</v>
       </c>
     </row>
     <row r="890">
@@ -11915,7 +11915,7 @@
         <v>2027</v>
       </c>
       <c r="D890">
-        <v>10.44633494162468</v>
+        <v>10.55887764769237</v>
       </c>
     </row>
     <row r="891">
@@ -11928,7 +11928,7 @@
         <v>2028</v>
       </c>
       <c r="D891">
-        <v>10.55884023715596</v>
+        <v>10.67153486206729</v>
       </c>
     </row>
     <row r="892">
@@ -11967,7 +11967,7 @@
         <v>2026</v>
       </c>
       <c r="D894">
-        <v>5.093271209589729</v>
+        <v>3.903495303597484</v>
       </c>
     </row>
     <row r="895">
@@ -11980,7 +11980,7 @@
         <v>2027</v>
       </c>
       <c r="D895">
-        <v>3.926718698520265</v>
+        <v>2.726575625221521</v>
       </c>
     </row>
     <row r="896">
@@ -11993,7 +11993,7 @@
         <v>2028</v>
       </c>
       <c r="D896">
-        <v>2.717082780526759</v>
+        <v>1.521177412761272</v>
       </c>
     </row>
     <row r="897">
@@ -12032,7 +12032,7 @@
         <v>2026</v>
       </c>
       <c r="D899">
-        <v>11.61350951295051</v>
+        <v>11.30881348759153</v>
       </c>
     </row>
     <row r="900">
@@ -12045,7 +12045,7 @@
         <v>2027</v>
       </c>
       <c r="D900">
-        <v>11.3085485830599</v>
+        <v>11.00517470281663</v>
       </c>
     </row>
     <row r="901">
@@ -12058,7 +12058,7 @@
         <v>2028</v>
       </c>
       <c r="D901">
-        <v>11.00521259490471</v>
+        <v>10.70164959430599</v>
       </c>
     </row>
     <row r="902">
@@ -12097,7 +12097,7 @@
         <v>2026</v>
       </c>
       <c r="D904">
-        <v>6.885567252843874</v>
+        <v>7.143499448617259</v>
       </c>
     </row>
     <row r="905">
@@ -12110,7 +12110,7 @@
         <v>2027</v>
       </c>
       <c r="D905">
-        <v>7.14539856035447</v>
+        <v>7.416887913983372</v>
       </c>
     </row>
     <row r="906">
@@ -12123,7 +12123,7 @@
         <v>2028</v>
       </c>
       <c r="D906">
-        <v>7.417257485624043</v>
+        <v>7.691385094271497</v>
       </c>
     </row>
     <row r="907">
@@ -12162,7 +12162,7 @@
         <v>2026</v>
       </c>
       <c r="D909">
-        <v>19.62862694359575</v>
+        <v>20.68230387265648</v>
       </c>
     </row>
     <row r="910">
@@ -12175,7 +12175,7 @@
         <v>2027</v>
       </c>
       <c r="D910">
-        <v>20.6810414586527</v>
+        <v>21.74074330404157</v>
       </c>
     </row>
     <row r="911">
@@ -12188,7 +12188,7 @@
         <v>2028</v>
       </c>
       <c r="D911">
-        <v>21.74092970600335</v>
+        <v>22.79974194131201</v>
       </c>
     </row>
     <row r="912">
@@ -12227,7 +12227,7 @@
         <v>2026</v>
       </c>
       <c r="D914">
-        <v>13.55435093245259</v>
+        <v>14.02732717756238</v>
       </c>
     </row>
     <row r="915">
@@ -12240,7 +12240,7 @@
         <v>2027</v>
       </c>
       <c r="D915">
-        <v>14.02702845046824</v>
+        <v>14.5018144358958</v>
       </c>
     </row>
     <row r="916">
@@ -12253,7 +12253,7 @@
         <v>2028</v>
       </c>
       <c r="D916">
-        <v>14.50185150721536</v>
+        <v>14.97641290818789</v>
       </c>
     </row>
     <row r="917">
@@ -12292,7 +12292,7 @@
         <v>2026</v>
       </c>
       <c r="D919">
-        <v>35.39496874470053</v>
+        <v>36.65010425054277</v>
       </c>
     </row>
     <row r="920">
@@ -12305,7 +12305,7 @@
         <v>2027</v>
       </c>
       <c r="D920">
-        <v>36.64686824145292</v>
+        <v>37.91723251657389</v>
       </c>
     </row>
     <row r="921">
@@ -12318,7 +12318,7 @@
         <v>2028</v>
       </c>
       <c r="D921">
-        <v>37.91771506840984</v>
+        <v>39.18580843811286</v>
       </c>
     </row>
     <row r="922">
@@ -12357,7 +12357,7 @@
         <v>2026</v>
       </c>
       <c r="D924">
-        <v>14.26739323999644</v>
+        <v>15.81544263521029</v>
       </c>
     </row>
     <row r="925">
@@ -12370,7 +12370,7 @@
         <v>2027</v>
       </c>
       <c r="D925">
-        <v>15.81780985191699</v>
+        <v>17.36734285916937</v>
       </c>
     </row>
     <row r="926">
@@ -12383,7 +12383,7 @@
         <v>2028</v>
       </c>
       <c r="D926">
-        <v>17.36561907484218</v>
+        <v>18.91407173014689</v>
       </c>
     </row>
     <row r="927">
@@ -12422,7 +12422,7 @@
         <v>2026</v>
       </c>
       <c r="D929">
-        <v>21.25458583379606</v>
+        <v>21.75992505579736</v>
       </c>
     </row>
     <row r="930">
@@ -12435,7 +12435,7 @@
         <v>2027</v>
       </c>
       <c r="D930">
-        <v>21.59430136408108</v>
+        <v>22.20528899743699</v>
       </c>
     </row>
     <row r="931">
@@ -12448,7 +12448,7 @@
         <v>2028</v>
       </c>
       <c r="D931">
-        <v>22.26807561059515</v>
+        <v>22.8390127785511</v>
       </c>
     </row>
     <row r="932">
@@ -12487,7 +12487,7 @@
         <v>2026</v>
       </c>
       <c r="D934">
-        <v>28.24978934817324</v>
+        <v>29.99057729696037</v>
       </c>
     </row>
     <row r="935">
@@ -12500,7 +12500,7 @@
         <v>2027</v>
       </c>
       <c r="D935">
-        <v>29.98999706033709</v>
+        <v>31.73382436340876</v>
       </c>
     </row>
     <row r="936">
@@ -12513,7 +12513,7 @@
         <v>2028</v>
       </c>
       <c r="D936">
-        <v>31.73390452730513</v>
+        <v>33.47731192154627</v>
       </c>
     </row>
     <row r="937">
@@ -12552,7 +12552,7 @@
         <v>2026</v>
       </c>
       <c r="D939">
-        <v>26.60875757580947</v>
+        <v>27.33646154158659</v>
       </c>
     </row>
     <row r="940">
@@ -12565,7 +12565,7 @@
         <v>2027</v>
       </c>
       <c r="D940">
-        <v>27.33677078564121</v>
+        <v>28.06192524328026</v>
       </c>
     </row>
     <row r="941">
@@ -12578,7 +12578,7 @@
         <v>2028</v>
       </c>
       <c r="D941">
-        <v>28.06189505641202</v>
+        <v>28.78729838436919</v>
       </c>
     </row>
     <row r="942">
@@ -12617,7 +12617,7 @@
         <v>2026</v>
       </c>
       <c r="D944">
-        <v>15.78116513855254</v>
+        <v>15.60245239092082</v>
       </c>
     </row>
     <row r="945">
@@ -12630,7 +12630,7 @@
         <v>2027</v>
       </c>
       <c r="D945">
-        <v>15.5840680091704</v>
+        <v>15.33130581703461</v>
       </c>
     </row>
     <row r="946">
@@ -12643,7 +12643,7 @@
         <v>2028</v>
       </c>
       <c r="D946">
-        <v>15.32223984819364</v>
+        <v>15.03296133662549</v>
       </c>
     </row>
     <row r="947">
@@ -12682,7 +12682,7 @@
         <v>2026</v>
       </c>
       <c r="D949">
-        <v>45.87413330816736</v>
+        <v>46.39403064453772</v>
       </c>
     </row>
     <row r="950">
@@ -12695,7 +12695,7 @@
         <v>2027</v>
       </c>
       <c r="D950">
-        <v>46.3940893663011</v>
+        <v>46.91319770325526</v>
       </c>
     </row>
     <row r="951">
@@ -12708,7 +12708,7 @@
         <v>2028</v>
       </c>
       <c r="D951">
-        <v>46.91319389910462</v>
+        <v>47.43235334952089</v>
       </c>
     </row>
     <row r="952">
@@ -12747,7 +12747,7 @@
         <v>2026</v>
       </c>
       <c r="D954">
-        <v>21.77572647597099</v>
+        <v>22.90191704694877</v>
       </c>
     </row>
     <row r="955">
@@ -12760,7 +12760,7 @@
         <v>2027</v>
       </c>
       <c r="D955">
-        <v>22.95178362743127</v>
+        <v>24.07227657666807</v>
       </c>
     </row>
     <row r="956">
@@ -12773,7 +12773,7 @@
         <v>2028</v>
       </c>
       <c r="D956">
-        <v>24.0486907150706</v>
+        <v>25.17187852159493</v>
       </c>
     </row>
     <row r="957">
@@ -12812,7 +12812,7 @@
         <v>2026</v>
       </c>
       <c r="D959">
-        <v>25.13367777302919</v>
+        <v>26.10814340296739</v>
       </c>
     </row>
     <row r="960">
@@ -12825,7 +12825,7 @@
         <v>2027</v>
       </c>
       <c r="D960">
-        <v>24.99774141062441</v>
+        <v>25.14054950315762</v>
       </c>
     </row>
     <row r="961">
@@ -12838,7 +12838,7 @@
         <v>2028</v>
       </c>
       <c r="D961">
-        <v>26.02813956755483</v>
+        <v>26.83572579653946</v>
       </c>
     </row>
     <row r="962">
@@ -12877,7 +12877,7 @@
         <v>2026</v>
       </c>
       <c r="D964">
-        <v>66.48221983199231</v>
+        <v>67.65007947282906</v>
       </c>
     </row>
     <row r="965">
@@ -12890,7 +12890,7 @@
         <v>2027</v>
       </c>
       <c r="D965">
-        <v>67.54556964529905</v>
+        <v>68.7320905978923</v>
       </c>
     </row>
     <row r="966">
@@ -12903,7 +12903,7 @@
         <v>2028</v>
       </c>
       <c r="D966">
-        <v>68.78006256587481</v>
+        <v>69.95801762690311</v>
       </c>
     </row>
     <row r="967">
@@ -12942,7 +12942,7 @@
         <v>2026</v>
       </c>
       <c r="D969">
-        <v>49.95257386700894</v>
+        <v>50.76292579365898</v>
       </c>
     </row>
     <row r="970">
@@ -12955,7 +12955,7 @@
         <v>2027</v>
       </c>
       <c r="D970">
-        <v>50.77020130308838</v>
+        <v>51.62681694990745</v>
       </c>
     </row>
     <row r="971">
@@ -12968,7 +12968,7 @@
         <v>2028</v>
       </c>
       <c r="D971">
-        <v>51.62848609303529</v>
+        <v>52.49571553553943</v>
       </c>
     </row>
     <row r="972">
@@ -13007,7 +13007,7 @@
         <v>2026</v>
       </c>
       <c r="D974">
-        <v>40.47224564571092</v>
+        <v>42.43079604129826</v>
       </c>
     </row>
     <row r="975">
@@ -13020,7 +13020,7 @@
         <v>2027</v>
       </c>
       <c r="D975">
-        <v>42.41998995561642</v>
+        <v>44.40579405270486</v>
       </c>
     </row>
     <row r="976">
@@ -13033,7 +13033,7 @@
         <v>2028</v>
       </c>
       <c r="D976">
-        <v>44.40818368540592</v>
+        <v>46.38796096221463</v>
       </c>
     </row>
     <row r="977">
@@ -13072,7 +13072,7 @@
         <v>2026</v>
       </c>
       <c r="D979">
-        <v>12.82347530060439</v>
+        <v>13.29673661695887</v>
       </c>
     </row>
     <row r="980">
@@ -13085,7 +13085,7 @@
         <v>2027</v>
       </c>
       <c r="D980">
-        <v>13.31536972072051</v>
+        <v>13.76891399063759</v>
       </c>
     </row>
     <row r="981">
@@ -13098,7 +13098,7 @@
         <v>2028</v>
       </c>
       <c r="D981">
-        <v>13.76282110313714</v>
+        <v>14.22281270181496</v>
       </c>
     </row>
     <row r="982">
@@ -13137,7 +13137,7 @@
         <v>2026</v>
       </c>
       <c r="D984">
-        <v>22.19303630683168</v>
+        <v>22.54704288179086</v>
       </c>
     </row>
     <row r="985">
@@ -13150,7 +13150,7 @@
         <v>2027</v>
       </c>
       <c r="D985">
-        <v>22.54518719881576</v>
+        <v>22.8994179106107</v>
       </c>
     </row>
     <row r="986">
@@ -13163,7 +13163,7 @@
         <v>2028</v>
       </c>
       <c r="D986">
-        <v>22.90029290917921</v>
+        <v>23.25441793513607</v>
       </c>
     </row>
     <row r="987">
@@ -13202,7 +13202,7 @@
         <v>2026</v>
       </c>
       <c r="D989">
-        <v>24.17899633035158</v>
+        <v>23.40627705488329</v>
       </c>
     </row>
     <row r="990">
@@ -13215,7 +13215,7 @@
         <v>2027</v>
       </c>
       <c r="D990">
-        <v>23.27196761027336</v>
+        <v>22.59521976534079</v>
       </c>
     </row>
     <row r="991">
@@ -13228,7 +13228,7 @@
         <v>2028</v>
       </c>
       <c r="D991">
-        <v>22.64469729102913</v>
+        <v>21.93259505286332</v>
       </c>
     </row>
     <row r="992">
@@ -13267,7 +13267,7 @@
         <v>2026</v>
       </c>
       <c r="D994">
-        <v>16.6047084902012</v>
+        <v>16.61990332421193</v>
       </c>
     </row>
     <row r="995">
@@ -13280,7 +13280,7 @@
         <v>2027</v>
       </c>
       <c r="D995">
-        <v>17.88650735945282</v>
+        <v>19.15529397743328</v>
       </c>
     </row>
     <row r="996">
@@ -13293,7 +13293,7 @@
         <v>2028</v>
       </c>
       <c r="D996">
-        <v>17.90156987357599</v>
+        <v>17.92951231908276</v>
       </c>
     </row>
     <row r="997">
@@ -13332,7 +13332,7 @@
         <v>2026</v>
       </c>
       <c r="D999">
-        <v>32.13256783763348</v>
+        <v>32.20943105067187</v>
       </c>
     </row>
     <row r="1000">
@@ -13345,7 +13345,7 @@
         <v>2027</v>
       </c>
       <c r="D1000">
-        <v>32.21235083982842</v>
+        <v>32.28904376668064</v>
       </c>
     </row>
     <row r="1001">
@@ -13358,7 +13358,7 @@
         <v>2028</v>
       </c>
       <c r="D1001">
-        <v>32.28762523740769</v>
+        <v>32.36440089487055</v>
       </c>
     </row>
     <row r="1002">
@@ -13397,7 +13397,7 @@
         <v>2026</v>
       </c>
       <c r="D1004">
-        <v>36.18389182971843</v>
+        <v>36.18601712226639</v>
       </c>
     </row>
     <row r="1005">
@@ -13410,7 +13410,7 @@
         <v>2027</v>
       </c>
       <c r="D1005">
-        <v>36.18972525895054</v>
+        <v>36.17670886828801</v>
       </c>
     </row>
     <row r="1006">
@@ -13423,7 +13423,7 @@
         <v>2028</v>
       </c>
       <c r="D1006">
-        <v>36.17609931495279</v>
+        <v>36.16557195430398</v>
       </c>
     </row>
     <row r="1007">
@@ -13462,7 +13462,7 @@
         <v>2026</v>
       </c>
       <c r="D1009">
-        <v>49.45513124130606</v>
+        <v>47.70519982531519</v>
       </c>
     </row>
     <row r="1010">
@@ -13475,7 +13475,7 @@
         <v>2027</v>
       </c>
       <c r="D1010">
-        <v>53.79367834904262</v>
+        <v>57.98895510844973</v>
       </c>
     </row>
     <row r="1011">
@@ -13488,7 +13488,7 @@
         <v>2028</v>
       </c>
       <c r="D1011">
-        <v>52.04045309160662</v>
+        <v>50.42720434105493</v>
       </c>
     </row>
     <row r="1012">
@@ -13527,7 +13527,7 @@
         <v>2026</v>
       </c>
       <c r="D1014">
-        <v>6.176496883790015</v>
+        <v>5.639577708810057</v>
       </c>
     </row>
     <row r="1015">
@@ -13540,7 +13540,7 @@
         <v>2027</v>
       </c>
       <c r="D1015">
-        <v>5.67295381033476</v>
+        <v>5.099798755548602</v>
       </c>
     </row>
     <row r="1016">
@@ -13553,7 +13553,7 @@
         <v>2028</v>
       </c>
       <c r="D1016">
-        <v>5.088982318130799</v>
+        <v>4.527570490033736</v>
       </c>
     </row>
     <row r="1017">
@@ -13592,7 +13592,7 @@
         <v>2026</v>
       </c>
       <c r="D1019">
-        <v>11.24228203053469</v>
+        <v>11.45437851944915</v>
       </c>
     </row>
     <row r="1020">
@@ -13605,7 +13605,7 @@
         <v>2027</v>
       </c>
       <c r="D1020">
-        <v>11.4543785200188</v>
+        <v>11.66647501994634</v>
       </c>
     </row>
     <row r="1021">
@@ -13618,7 +13618,7 @@
         <v>2028</v>
       </c>
       <c r="D1021">
-        <v>11.6664750199792</v>
+        <v>11.87857152054213</v>
       </c>
     </row>
     <row r="1022">
@@ -13657,7 +13657,7 @@
         <v>2026</v>
       </c>
       <c r="D1024">
-        <v>32.97756988549707</v>
+        <v>36.0472351039645</v>
       </c>
     </row>
     <row r="1025">
@@ -13670,7 +13670,7 @@
         <v>2027</v>
       </c>
       <c r="D1025">
-        <v>34.93365432780433</v>
+        <v>36.93356981617224</v>
       </c>
     </row>
     <row r="1026">
@@ -13683,7 +13683,7 @@
         <v>2028</v>
       </c>
       <c r="D1026">
-        <v>38.00497942269767</v>
+        <v>41.03413334795626</v>
       </c>
     </row>
     <row r="1027">
@@ -13722,7 +13722,7 @@
         <v>2026</v>
       </c>
       <c r="D1029">
-        <v>8.621064684047537</v>
+        <v>8.519801256829446</v>
       </c>
     </row>
     <row r="1030">
@@ -13735,7 +13735,7 @@
         <v>2027</v>
       </c>
       <c r="D1030">
-        <v>9.685448955505516</v>
+        <v>10.6147699447426</v>
       </c>
     </row>
     <row r="1031">
@@ -13748,7 +13748,7 @@
         <v>2028</v>
       </c>
       <c r="D1031">
-        <v>9.570160821436946</v>
+        <v>9.575911262738787</v>
       </c>
     </row>
     <row r="1032">
@@ -13787,7 +13787,7 @@
         <v>2026</v>
       </c>
       <c r="D1034">
-        <v>22.74935381177296</v>
+        <v>23.34486356157476</v>
       </c>
     </row>
     <row r="1035">
@@ -13800,7 +13800,7 @@
         <v>2027</v>
       </c>
       <c r="D1035">
-        <v>23.09740885399613</v>
+        <v>23.46600350998036</v>
       </c>
     </row>
     <row r="1036">
@@ -13813,7 +13813,7 @@
         <v>2028</v>
       </c>
       <c r="D1036">
-        <v>23.69449280033816</v>
+        <v>24.27261132945937</v>
       </c>
     </row>
     <row r="1037">
@@ -13852,7 +13852,7 @@
         <v>2026</v>
       </c>
       <c r="D1039">
-        <v>18.05549987682165</v>
+        <v>18.8810846199229</v>
       </c>
     </row>
     <row r="1040">
@@ -13865,7 +13865,7 @@
         <v>2027</v>
       </c>
       <c r="D1040">
-        <v>17.55573860835981</v>
+        <v>17.15979798921955</v>
       </c>
     </row>
     <row r="1041">
@@ -13878,7 +13878,7 @@
         <v>2028</v>
       </c>
       <c r="D1041">
-        <v>18.38886531806339</v>
+        <v>19.12571334504772</v>
       </c>
     </row>
     <row r="1042">
@@ -13917,7 +13917,7 @@
         <v>2026</v>
       </c>
       <c r="D1044">
-        <v>19.7793640905208</v>
+        <v>19.48149785517648</v>
       </c>
     </row>
     <row r="1045">
@@ -13930,7 +13930,7 @@
         <v>2027</v>
       </c>
       <c r="D1045">
-        <v>19.60049693012006</v>
+        <v>19.21049384907398</v>
       </c>
     </row>
     <row r="1046">
@@ -13943,7 +13943,7 @@
         <v>2028</v>
       </c>
       <c r="D1046">
-        <v>19.16759994195526</v>
+        <v>18.81080812161533</v>
       </c>
     </row>
     <row r="1047">
@@ -13982,7 +13982,7 @@
         <v>2026</v>
       </c>
       <c r="D1049">
-        <v>30.02337272454584</v>
+        <v>30.37554050991061</v>
       </c>
     </row>
     <row r="1050">
@@ -13995,7 +13995,7 @@
         <v>2027</v>
       </c>
       <c r="D1050">
-        <v>26.43435980247445</v>
+        <v>23.22032689669096</v>
       </c>
     </row>
     <row r="1051">
@@ -14008,7 +14008,7 @@
         <v>2028</v>
       </c>
       <c r="D1051">
-        <v>26.81910515424966</v>
+        <v>26.8614480561474</v>
       </c>
     </row>
     <row r="1052">
@@ -14047,7 +14047,7 @@
         <v>2026</v>
       </c>
       <c r="D1054">
-        <v>27.86990434950891</v>
+        <v>30.15058114000988</v>
       </c>
     </row>
     <row r="1055">
@@ -14060,7 +14060,7 @@
         <v>2027</v>
       </c>
       <c r="D1055">
-        <v>30.03021238231095</v>
+        <v>32.2086160995086</v>
       </c>
     </row>
     <row r="1056">
@@ -14073,7 +14073,7 @@
         <v>2028</v>
       </c>
       <c r="D1056">
-        <v>32.31325406728441</v>
+        <v>34.58056496233475</v>
       </c>
     </row>
     <row r="1057">
@@ -14112,7 +14112,7 @@
         <v>2026</v>
       </c>
       <c r="D1059">
-        <v>27.27158358459064</v>
+        <v>26.34683553877415</v>
       </c>
     </row>
     <row r="1060">
@@ -14125,7 +14125,7 @@
         <v>2027</v>
       </c>
       <c r="D1060">
-        <v>26.30919006887326</v>
+        <v>25.3644398714543</v>
       </c>
     </row>
     <row r="1061">
@@ -14138,7 +14138,7 @@
         <v>2028</v>
       </c>
       <c r="D1061">
-        <v>25.39007221844932</v>
+        <v>24.4589412451195</v>
       </c>
     </row>
     <row r="1062">
@@ -14177,7 +14177,7 @@
         <v>2026</v>
       </c>
       <c r="D1064">
-        <v>35.48849698310146</v>
+        <v>35.51531597663823</v>
       </c>
     </row>
     <row r="1065">
@@ -14190,7 +14190,7 @@
         <v>2027</v>
       </c>
       <c r="D1065">
-        <v>35.59396635067183</v>
+        <v>35.61467973641365</v>
       </c>
     </row>
     <row r="1066">
@@ -14203,7 +14203,7 @@
         <v>2028</v>
       </c>
       <c r="D1066">
-        <v>35.57682391799711</v>
+        <v>35.60047604093946</v>
       </c>
     </row>
     <row r="1067">
@@ -14242,7 +14242,7 @@
         <v>2026</v>
       </c>
       <c r="D1069">
-        <v>35.12991515373746</v>
+        <v>34.13468663085885</v>
       </c>
     </row>
     <row r="1070">
@@ -14255,7 +14255,7 @@
         <v>2027</v>
       </c>
       <c r="D1070">
-        <v>34.463388340619</v>
+        <v>33.45994975895523</v>
       </c>
     </row>
     <row r="1071">
@@ -14268,7 +14268,7 @@
         <v>2028</v>
       </c>
       <c r="D1071">
-        <v>33.29762610187678</v>
+        <v>32.29824191581626</v>
       </c>
     </row>
     <row r="1072">
@@ -14307,7 +14307,7 @@
         <v>2026</v>
       </c>
       <c r="D1074">
-        <v>26.66483071947873</v>
+        <v>28.26246493023691</v>
       </c>
     </row>
     <row r="1075">
@@ -14320,7 +14320,7 @@
         <v>2027</v>
       </c>
       <c r="D1075">
-        <v>28.28798834467194</v>
+        <v>29.88991869874792</v>
       </c>
     </row>
     <row r="1076">
@@ -14333,7 +14333,7 @@
         <v>2028</v>
       </c>
       <c r="D1076">
-        <v>29.87598425742953</v>
+        <v>31.47556914330377</v>
       </c>
     </row>
     <row r="1077">
@@ -14372,7 +14372,7 @@
         <v>2026</v>
       </c>
       <c r="D1079">
-        <v>10.2206864808109</v>
+        <v>10.56530372307002</v>
       </c>
     </row>
     <row r="1080">
@@ -14385,7 +14385,7 @@
         <v>2027</v>
       </c>
       <c r="D1080">
-        <v>10.56530341610627</v>
+        <v>10.90992153159126</v>
       </c>
     </row>
     <row r="1081">
@@ -14398,7 +14398,7 @@
         <v>2028</v>
       </c>
       <c r="D1081">
-        <v>10.90992159495174</v>
+        <v>11.25453953019393</v>
       </c>
     </row>
     <row r="1082">
@@ -14437,7 +14437,7 @@
         <v>2026</v>
       </c>
       <c r="D1084">
-        <v>24.42096117196194</v>
+        <v>25.91973899694727</v>
       </c>
     </row>
     <row r="1085">
@@ -14450,7 +14450,7 @@
         <v>2027</v>
       </c>
       <c r="D1085">
-        <v>26.00920262720808</v>
+        <v>27.48979902281451</v>
       </c>
     </row>
     <row r="1086">
@@ -14463,7 +14463,7 @@
         <v>2028</v>
       </c>
       <c r="D1086">
-        <v>27.44919329841199</v>
+        <v>28.93804187547418</v>
       </c>
     </row>
     <row r="1087">
@@ -14502,7 +14502,7 @@
         <v>2026</v>
       </c>
       <c r="D1089">
-        <v>17.68521986537435</v>
+        <v>18.1480673015856</v>
       </c>
     </row>
     <row r="1090">
@@ -14515,7 +14515,7 @@
         <v>2027</v>
       </c>
       <c r="D1090">
-        <v>18.13847999960712</v>
+        <v>18.60482755370536</v>
       </c>
     </row>
     <row r="1091">
@@ -14528,7 +14528,7 @@
         <v>2028</v>
       </c>
       <c r="D1091">
-        <v>18.60888124661763</v>
+        <v>19.07374888456193</v>
       </c>
     </row>
     <row r="1092">
@@ -14567,7 +14567,7 @@
         <v>2026</v>
       </c>
       <c r="D1094">
-        <v>20.52345245611379</v>
+        <v>20.7615816667143</v>
       </c>
     </row>
     <row r="1095">
@@ -14580,7 +14580,7 @@
         <v>2027</v>
       </c>
       <c r="D1095">
-        <v>20.75771213842364</v>
+        <v>21.00257675528023</v>
       </c>
     </row>
     <row r="1096">
@@ -14593,7 +14593,7 @@
         <v>2028</v>
       </c>
       <c r="D1096">
-        <v>21.00361121502914</v>
+        <v>21.24667522309286</v>
       </c>
     </row>
     <row r="1097">
@@ -14632,7 +14632,7 @@
         <v>2026</v>
       </c>
       <c r="D1099">
-        <v>14.77206122694013</v>
+        <v>14.42730636667173</v>
       </c>
     </row>
     <row r="1100">
@@ -14645,7 +14645,7 @@
         <v>2027</v>
       </c>
       <c r="D1100">
-        <v>14.69203205940872</v>
+        <v>14.39097337361832</v>
       </c>
     </row>
     <row r="1101">
@@ -14658,7 +14658,7 @@
         <v>2028</v>
       </c>
       <c r="D1101">
-        <v>14.24670380983662</v>
+        <v>13.9218316892198</v>
       </c>
     </row>
     <row r="1102">
@@ -14697,7 +14697,7 @@
         <v>2026</v>
       </c>
       <c r="D1104">
-        <v>20.34159056424207</v>
+        <v>21.16556519406137</v>
       </c>
     </row>
     <row r="1105">
@@ -14710,7 +14710,7 @@
         <v>2027</v>
       </c>
       <c r="D1105">
-        <v>20.98788865144303</v>
+        <v>21.81524290694687</v>
       </c>
     </row>
     <row r="1106">
@@ -14723,7 +14723,7 @@
         <v>2028</v>
       </c>
       <c r="D1106">
-        <v>21.90324423170964</v>
+        <v>22.72892459412068</v>
       </c>
     </row>
     <row r="1107">
@@ -14762,7 +14762,7 @@
         <v>2026</v>
       </c>
       <c r="D1109">
-        <v>17.75762074882718</v>
+        <v>17.81849754765986</v>
       </c>
     </row>
     <row r="1110">
@@ -14775,7 +14775,7 @@
         <v>2027</v>
       </c>
       <c r="D1110">
-        <v>17.84825013025597</v>
+        <v>17.86607993270891</v>
       </c>
     </row>
     <row r="1111">
@@ -14788,7 +14788,7 @@
         <v>2028</v>
       </c>
       <c r="D1111">
-        <v>17.85744807007853</v>
+        <v>17.88776672986682</v>
       </c>
     </row>
     <row r="1112">
@@ -14827,7 +14827,7 @@
         <v>2026</v>
       </c>
       <c r="D1114">
-        <v>31.02782415799821</v>
+        <v>33.08689107088257</v>
       </c>
     </row>
     <row r="1115">
@@ -14840,7 +14840,7 @@
         <v>2027</v>
       </c>
       <c r="D1115">
-        <v>32.20717561853308</v>
+        <v>33.94520602113275</v>
       </c>
     </row>
     <row r="1116">
@@ -14853,7 +14853,7 @@
         <v>2028</v>
       </c>
       <c r="D1116">
-        <v>34.48323598016746</v>
+        <v>36.41761084848704</v>
       </c>
     </row>
     <row r="1117">
@@ -14892,7 +14892,7 @@
         <v>2026</v>
       </c>
       <c r="D1119">
-        <v>32.44240860509779</v>
+        <v>33.26650745322458</v>
       </c>
     </row>
     <row r="1120">
@@ -14905,7 +14905,7 @@
         <v>2027</v>
       </c>
       <c r="D1120">
-        <v>33.23849644277092</v>
+        <v>33.92832516867912</v>
       </c>
     </row>
     <row r="1121">
@@ -14918,7 +14918,7 @@
         <v>2028</v>
       </c>
       <c r="D1121">
-        <v>33.9182978748089</v>
+        <v>34.56006100252301</v>
       </c>
     </row>
     <row r="1122">
@@ -14957,7 +14957,7 @@
         <v>2026</v>
       </c>
       <c r="D1124">
-        <v>34.820152138099</v>
+        <v>33.89599803435455</v>
       </c>
     </row>
     <row r="1125">
@@ -14970,7 +14970,7 @@
         <v>2027</v>
       </c>
       <c r="D1125">
-        <v>33.99173618127534</v>
+        <v>33.43665970868896</v>
       </c>
     </row>
     <row r="1126">
@@ -14983,7 +14983,7 @@
         <v>2028</v>
       </c>
       <c r="D1126">
-        <v>33.4882685136356</v>
+        <v>33.13214779786327</v>
       </c>
     </row>
     <row r="1127">
@@ -15022,7 +15022,7 @@
         <v>2026</v>
       </c>
       <c r="D1129">
-        <v>16.3041258503303</v>
+        <v>15.85815788762604</v>
       </c>
     </row>
     <row r="1130">
@@ -15035,7 +15035,7 @@
         <v>2027</v>
       </c>
       <c r="D1130">
-        <v>16.27566881599533</v>
+        <v>16.18773924151845</v>
       </c>
     </row>
     <row r="1131">
@@ -15048,7 +15048,7 @@
         <v>2028</v>
       </c>
       <c r="D1131">
-        <v>15.82228553753187</v>
+        <v>15.42095948345112</v>
       </c>
     </row>
     <row r="1132">
@@ -15087,7 +15087,7 @@
         <v>2026</v>
       </c>
       <c r="D1134">
-        <v>49.71999827947915</v>
+        <v>51.64867528452586</v>
       </c>
     </row>
     <row r="1135">
@@ -15100,7 +15100,7 @@
         <v>2027</v>
       </c>
       <c r="D1135">
-        <v>51.64787543769317</v>
+        <v>53.58392478442253</v>
       </c>
     </row>
     <row r="1136">
@@ -15113,7 +15113,7 @@
         <v>2028</v>
       </c>
       <c r="D1136">
-        <v>53.5839960898656</v>
+        <v>55.51938820064842</v>
       </c>
     </row>
     <row r="1137">
@@ -15152,7 +15152,7 @@
         <v>2026</v>
       </c>
       <c r="D1139">
-        <v>13.92275010909946</v>
+        <v>11.98341244243048</v>
       </c>
     </row>
     <row r="1140">
@@ -15165,7 +15165,7 @@
         <v>2027</v>
       </c>
       <c r="D1140">
-        <v>12.54298713000521</v>
+        <v>11.0917892918583</v>
       </c>
     </row>
     <row r="1141">
@@ -15178,7 +15178,7 @@
         <v>2028</v>
       </c>
       <c r="D1141">
-        <v>10.59556251898627</v>
+        <v>8.711485822670028</v>
       </c>
     </row>
     <row r="1142">
@@ -15217,7 +15217,7 @@
         <v>2026</v>
       </c>
       <c r="D1144">
-        <v>23.59557177159133</v>
+        <v>23.79001531534692</v>
       </c>
     </row>
     <row r="1145">
@@ -15230,7 +15230,7 @@
         <v>2027</v>
       </c>
       <c r="D1145">
-        <v>26.60818171389462</v>
+        <v>29.354446263007</v>
       </c>
     </row>
     <row r="1146">
@@ -15243,7 +15243,7 @@
         <v>2028</v>
       </c>
       <c r="D1146">
-        <v>26.77962652291882</v>
+        <v>27.19441799040255</v>
       </c>
     </row>
     <row r="1147">
@@ -15282,7 +15282,7 @@
         <v>2026</v>
       </c>
       <c r="D1149">
-        <v>29.40374665985931</v>
+        <v>27.9153800141398</v>
       </c>
     </row>
     <row r="1150">
@@ -15295,7 +15295,7 @@
         <v>2027</v>
       </c>
       <c r="D1150">
-        <v>28.02793190837472</v>
+        <v>26.97980114242226</v>
       </c>
     </row>
     <row r="1151">
@@ -15308,7 +15308,7 @@
         <v>2028</v>
       </c>
       <c r="D1151">
-        <v>27.03868556463692</v>
+        <v>26.22087553734871</v>
       </c>
     </row>
     <row r="1152">
@@ -15347,7 +15347,7 @@
         <v>2026</v>
       </c>
       <c r="D1154">
-        <v>20.39504469928868</v>
+        <v>19.43783055245086</v>
       </c>
     </row>
     <row r="1155">
@@ -15360,7 +15360,7 @@
         <v>2027</v>
       </c>
       <c r="D1155">
-        <v>19.43796719433235</v>
+        <v>18.47828457732124</v>
       </c>
     </row>
     <row r="1156">
@@ -15373,7 +15373,7 @@
         <v>2028</v>
       </c>
       <c r="D1156">
-        <v>18.47827776744544</v>
+        <v>17.51871817256423</v>
       </c>
     </row>
     <row r="1157">
@@ -15412,7 +15412,7 @@
         <v>2026</v>
       </c>
       <c r="D1159">
-        <v>36.3923628617811</v>
+        <v>36.38925097300287</v>
       </c>
     </row>
     <row r="1160">
@@ -15425,7 +15425,7 @@
         <v>2027</v>
       </c>
       <c r="D1160">
-        <v>36.62721937887765</v>
+        <v>36.78450564681157</v>
       </c>
     </row>
     <row r="1161">
@@ -15438,7 +15438,7 @@
         <v>2028</v>
       </c>
       <c r="D1161">
-        <v>36.60503805610427</v>
+        <v>36.64135754849838</v>
       </c>
     </row>
     <row r="1162">
@@ -15477,7 +15477,7 @@
         <v>2026</v>
       </c>
       <c r="D1164">
-        <v>10.10427811334208</v>
+        <v>9.766295316706827</v>
       </c>
     </row>
     <row r="1165">
@@ -15490,7 +15490,7 @@
         <v>2027</v>
       </c>
       <c r="D1165">
-        <v>9.765674004020395</v>
+        <v>9.431379921284321</v>
       </c>
     </row>
     <row r="1166">
@@ -15503,7 +15503,7 @@
         <v>2028</v>
       </c>
       <c r="D1166">
-        <v>9.431458202139284</v>
+        <v>9.096699368426702</v>
       </c>
     </row>
     <row r="1167">
@@ -15542,7 +15542,7 @@
         <v>2026</v>
       </c>
       <c r="D1169">
-        <v>16.16169811104909</v>
+        <v>15.49553105045801</v>
       </c>
     </row>
     <row r="1170">
@@ -15555,7 +15555,7 @@
         <v>2027</v>
       </c>
       <c r="D1170">
-        <v>14.71946291225115</v>
+        <v>13.71825020048114</v>
       </c>
     </row>
     <row r="1171">
@@ -15568,7 +15568,7 @@
         <v>2028</v>
       </c>
       <c r="D1171">
-        <v>14.2131038643352</v>
+        <v>13.42553034206646</v>
       </c>
     </row>
     <row r="1172">
@@ -15607,7 +15607,7 @@
         <v>2026</v>
       </c>
       <c r="D1174">
-        <v>28.57122871880586</v>
+        <v>30.59409384248575</v>
       </c>
     </row>
     <row r="1175">
@@ -15620,7 +15620,7 @@
         <v>2027</v>
       </c>
       <c r="D1175">
-        <v>30.45211143995593</v>
+        <v>31.97854492844158</v>
       </c>
     </row>
     <row r="1176">
@@ -15633,7 +15633,7 @@
         <v>2028</v>
       </c>
       <c r="D1176">
-        <v>31.88366422346111</v>
+        <v>33.07835389945598</v>
       </c>
     </row>
     <row r="1177">
@@ -15672,7 +15672,7 @@
         <v>2026</v>
       </c>
       <c r="D1179">
-        <v>35.67857692887986</v>
+        <v>35.67369024077922</v>
       </c>
     </row>
     <row r="1180">
@@ -15685,7 +15685,7 @@
         <v>2027</v>
       </c>
       <c r="D1180">
-        <v>35.6745892888244</v>
+        <v>35.66273405834055</v>
       </c>
     </row>
     <row r="1181">
@@ -15698,7 +15698,7 @@
         <v>2028</v>
       </c>
       <c r="D1181">
-        <v>35.66264185796181</v>
+        <v>35.65150127476566</v>
       </c>
     </row>
     <row r="1182">
@@ -15737,7 +15737,7 @@
         <v>2026</v>
       </c>
       <c r="D1184">
-        <v>38.09997358463583</v>
+        <v>38.04967160214135</v>
       </c>
     </row>
     <row r="1185">
@@ -15750,7 +15750,7 @@
         <v>2027</v>
       </c>
       <c r="D1185">
-        <v>38.50967181404278</v>
+        <v>38.86746579564785</v>
       </c>
     </row>
     <row r="1186">
@@ -15763,7 +15763,7 @@
         <v>2028</v>
       </c>
       <c r="D1186">
-        <v>38.45410703125654</v>
+        <v>38.44518369598044</v>
       </c>
     </row>
     <row r="1187">
@@ -15802,7 +15802,7 @@
         <v>2026</v>
       </c>
       <c r="D1189">
-        <v>25.92362043111682</v>
+        <v>25.06897985789137</v>
       </c>
     </row>
     <row r="1190">
@@ -15815,7 +15815,7 @@
         <v>2027</v>
       </c>
       <c r="D1190">
-        <v>25.43590888718975</v>
+        <v>24.8900992541713</v>
       </c>
     </row>
     <row r="1191">
@@ -15828,7 +15828,7 @@
         <v>2028</v>
       </c>
       <c r="D1191">
-        <v>24.57332673139222</v>
+        <v>23.76090108211398</v>
       </c>
     </row>
     <row r="1192">
@@ -15867,7 +15867,7 @@
         <v>2026</v>
       </c>
       <c r="D1194">
-        <v>18.51212774496856</v>
+        <v>18.57015024467745</v>
       </c>
     </row>
     <row r="1195">
@@ -15880,7 +15880,7 @@
         <v>2027</v>
       </c>
       <c r="D1195">
-        <v>18.56983304420901</v>
+        <v>18.62949681521766</v>
       </c>
     </row>
     <row r="1196">
@@ -15893,7 +15893,7 @@
         <v>2028</v>
       </c>
       <c r="D1196">
-        <v>18.62954102902647</v>
+        <v>18.68897602718429</v>
       </c>
     </row>
     <row r="1197">
@@ -15932,7 +15932,7 @@
         <v>2026</v>
       </c>
       <c r="D1199">
-        <v>37.28838648026161</v>
+        <v>37.80792702503172</v>
       </c>
     </row>
     <row r="1200">
@@ -15945,7 +15945,7 @@
         <v>2027</v>
       </c>
       <c r="D1200">
-        <v>38.53914339363828</v>
+        <v>39.41265143653408</v>
       </c>
     </row>
     <row r="1201">
@@ -15958,7 +15958,7 @@
         <v>2028</v>
       </c>
       <c r="D1201">
-        <v>38.93029316415527</v>
+        <v>39.57030103090003</v>
       </c>
     </row>
     <row r="1202">
@@ -15997,7 +15997,7 @@
         <v>2026</v>
       </c>
       <c r="D1204">
-        <v>40.55539958427025</v>
+        <v>43.09927415744846</v>
       </c>
     </row>
     <row r="1205">
@@ -16010,7 +16010,7 @@
         <v>2027</v>
       </c>
       <c r="D1205">
-        <v>42.43124215320907</v>
+        <v>44.44573999865059</v>
       </c>
     </row>
     <row r="1206">
@@ -16023,7 +16023,7 @@
         <v>2028</v>
       </c>
       <c r="D1206">
-        <v>44.99894911616335</v>
+        <v>47.45183319239099</v>
       </c>
     </row>
     <row r="1207">
@@ -16062,7 +16062,7 @@
         <v>2026</v>
       </c>
       <c r="D1209">
-        <v>34.93022895460916</v>
+        <v>35.43913658895615</v>
       </c>
     </row>
     <row r="1210">
@@ -16075,7 +16075,7 @@
         <v>2027</v>
       </c>
       <c r="D1210">
-        <v>35.45683985494231</v>
+        <v>35.92360844144859</v>
       </c>
     </row>
     <row r="1211">
@@ -16088,7 +16088,7 @@
         <v>2028</v>
       </c>
       <c r="D1211">
-        <v>35.91956687483276</v>
+        <v>36.39595559409356</v>
       </c>
     </row>
     <row r="1212">
@@ -16127,7 +16127,7 @@
         <v>2026</v>
       </c>
       <c r="D1214">
-        <v>38.77461893764018</v>
+        <v>39.88384975986258</v>
       </c>
     </row>
     <row r="1215">
@@ -16140,7 +16140,7 @@
         <v>2027</v>
       </c>
       <c r="D1215">
-        <v>39.88401689903673</v>
+        <v>40.99078215351432</v>
       </c>
     </row>
     <row r="1216">
@@ -16153,7 +16153,7 @@
         <v>2028</v>
       </c>
       <c r="D1216">
-        <v>40.99077217600034</v>
+        <v>42.09768461462413</v>
       </c>
     </row>
     <row r="1217">
@@ -16192,7 +16192,7 @@
         <v>2026</v>
       </c>
       <c r="D1219">
-        <v>47.30446016948645</v>
+        <v>48.14015733541047</v>
       </c>
     </row>
     <row r="1220">
@@ -16205,7 +16205,7 @@
         <v>2027</v>
       </c>
       <c r="D1220">
-        <v>48.14015564798873</v>
+        <v>48.97583963474227</v>
       </c>
     </row>
     <row r="1221">
@@ -16218,7 +16218,7 @@
         <v>2028</v>
       </c>
       <c r="D1221">
-        <v>48.97583934432028</v>
+        <v>49.81152106280813</v>
       </c>
     </row>
     <row r="1222">
@@ -16257,7 +16257,7 @@
         <v>2026</v>
       </c>
       <c r="D1224">
-        <v>40.3058417176971</v>
+        <v>39.65633188514489</v>
       </c>
     </row>
     <row r="1225">
@@ -16270,7 +16270,7 @@
         <v>2027</v>
       </c>
       <c r="D1225">
-        <v>40.1800611421863</v>
+        <v>39.93983950512749</v>
       </c>
     </row>
     <row r="1226">
@@ -16283,7 +16283,7 @@
         <v>2028</v>
       </c>
       <c r="D1226">
-        <v>39.51002895660898</v>
+        <v>38.93391547955459</v>
       </c>
     </row>
     <row r="1227">
@@ -16322,7 +16322,7 @@
         <v>2026</v>
       </c>
       <c r="D1229">
-        <v>39.20744695648235</v>
+        <v>40.84667259948019</v>
       </c>
     </row>
     <row r="1230">
@@ -16335,7 +16335,7 @@
         <v>2027</v>
       </c>
       <c r="D1230">
-        <v>40.81184299035292</v>
+        <v>42.42566811485619</v>
       </c>
     </row>
     <row r="1231">
@@ -16348,7 +16348,7 @@
         <v>2028</v>
       </c>
       <c r="D1231">
-        <v>42.45307745310014</v>
+        <v>44.08689164496404</v>
       </c>
     </row>
     <row r="1232">
@@ -16387,7 +16387,7 @@
         <v>2026</v>
       </c>
       <c r="D1234">
-        <v>48.60709683154908</v>
+        <v>50.06372005172138</v>
       </c>
     </row>
     <row r="1235">
@@ -16400,7 +16400,7 @@
         <v>2027</v>
       </c>
       <c r="D1235">
-        <v>48.00482220424516</v>
+        <v>48.2759211599671</v>
       </c>
     </row>
     <row r="1236">
@@ -16413,7 +16413,7 @@
         <v>2028</v>
       </c>
       <c r="D1236">
-        <v>49.72157871480553</v>
+        <v>50.82509493272811</v>
       </c>
     </row>
     <row r="1237">
@@ -16452,7 +16452,7 @@
         <v>2026</v>
       </c>
       <c r="D1239">
-        <v>47.82291527172531</v>
+        <v>48.610422796963</v>
       </c>
     </row>
     <row r="1240">
@@ -16465,7 +16465,7 @@
         <v>2027</v>
       </c>
       <c r="D1240">
-        <v>48.52227034962171</v>
+        <v>49.34534057184364</v>
       </c>
     </row>
     <row r="1241">
@@ -16478,7 +16478,7 @@
         <v>2028</v>
       </c>
       <c r="D1241">
-        <v>49.38201845122634</v>
+        <v>50.19029198487236</v>
       </c>
     </row>
     <row r="1242">
@@ -16517,7 +16517,7 @@
         <v>2026</v>
       </c>
       <c r="D1244">
-        <v>56.88661793803981</v>
+        <v>56.12609745538661</v>
       </c>
     </row>
     <row r="1245">
@@ -16530,7 +16530,7 @@
         <v>2027</v>
       </c>
       <c r="D1245">
-        <v>57.80775385927131</v>
+        <v>58.6659121964182</v>
       </c>
     </row>
     <row r="1246">
@@ -16543,7 +16543,7 @@
         <v>2028</v>
       </c>
       <c r="D1246">
-        <v>57.0449600194988</v>
+        <v>56.34287040669159</v>
       </c>
     </row>
     <row r="1247">
@@ -16582,7 +16582,7 @@
         <v>2026</v>
       </c>
       <c r="D1249">
-        <v>42.89912437787527</v>
+        <v>43.02756094275903</v>
       </c>
     </row>
     <row r="1250">
@@ -16595,7 +16595,7 @@
         <v>2027</v>
       </c>
       <c r="D1250">
-        <v>43.0311697988752</v>
+        <v>43.14434480812746</v>
       </c>
     </row>
     <row r="1251">
@@ -16608,7 +16608,7 @@
         <v>2028</v>
       </c>
       <c r="D1251">
-        <v>43.14376543683537</v>
+        <v>43.25939055961965</v>
       </c>
     </row>
     <row r="1252">
@@ -16647,7 +16647,7 @@
         <v>2026</v>
       </c>
       <c r="D1254">
-        <v>41.784872904956</v>
+        <v>39.98089174314029</v>
       </c>
     </row>
     <row r="1255">
@@ -16660,7 +16660,7 @@
         <v>2027</v>
       </c>
       <c r="D1255">
-        <v>39.59504395583323</v>
+        <v>37.44484779886272</v>
       </c>
     </row>
     <row r="1256">
@@ -16673,7 +16673,7 @@
         <v>2028</v>
       </c>
       <c r="D1256">
-        <v>37.79475452118348</v>
+        <v>35.95852402154746</v>
       </c>
     </row>
     <row r="1257">
@@ -16712,7 +16712,7 @@
         <v>2026</v>
       </c>
       <c r="D1259">
-        <v>42.25614051200317</v>
+        <v>39.46179694677407</v>
       </c>
     </row>
     <row r="1260">
@@ -16725,7 +16725,7 @@
         <v>2027</v>
       </c>
       <c r="D1260">
-        <v>42.28607050364445</v>
+        <v>42.28497346826302</v>
       </c>
     </row>
     <row r="1261">
@@ -16738,7 +16738,7 @@
         <v>2028</v>
       </c>
       <c r="D1261">
-        <v>39.49138978427779</v>
+        <v>36.72739893779627</v>
       </c>
     </row>
     <row r="1262">
@@ -16777,7 +16777,7 @@
         <v>2026</v>
       </c>
       <c r="D1264">
-        <v>12.95851032874052</v>
+        <v>13.20120183895864</v>
       </c>
     </row>
     <row r="1265">
@@ -16790,7 +16790,7 @@
         <v>2027</v>
       </c>
       <c r="D1265">
-        <v>13.20111558947299</v>
+        <v>13.44440573442224</v>
       </c>
     </row>
     <row r="1266">
@@ -16803,7 +16803,7 @@
         <v>2028</v>
       </c>
       <c r="D1266">
-        <v>13.44441538122376</v>
+        <v>13.6876385702904</v>
       </c>
     </row>
     <row r="1267">
@@ -16842,7 +16842,7 @@
         <v>2026</v>
       </c>
       <c r="D1269">
-        <v>60.7480642412664</v>
+        <v>63.82430410024669</v>
       </c>
     </row>
     <row r="1270">
@@ -16855,7 +16855,7 @@
         <v>2027</v>
       </c>
       <c r="D1270">
-        <v>63.88862528174138</v>
+        <v>66.99827199154203</v>
       </c>
     </row>
     <row r="1271">
@@ -16868,7 +16868,7 @@
         <v>2028</v>
       </c>
       <c r="D1271">
-        <v>66.95483006221708</v>
+        <v>70.04191409486251</v>
       </c>
     </row>
     <row r="1272">
@@ -16907,7 +16907,7 @@
         <v>2026</v>
       </c>
       <c r="D1274">
-        <v>80.26790965933793</v>
+        <v>80.91683019468732</v>
       </c>
     </row>
     <row r="1275">
@@ -16920,7 +16920,7 @@
         <v>2027</v>
       </c>
       <c r="D1275">
-        <v>82.67951854646431</v>
+        <v>84.87017246914549</v>
       </c>
     </row>
     <row r="1276">
@@ -16933,7 +16933,7 @@
         <v>2028</v>
       </c>
       <c r="D1276">
-        <v>83.30382724967951</v>
+        <v>84.12447908520571</v>
       </c>
     </row>
     <row r="1277">
@@ -16972,7 +16972,7 @@
         <v>2026</v>
       </c>
       <c r="D1279">
-        <v>61.02633163331186</v>
+        <v>63.92645494599514</v>
       </c>
     </row>
     <row r="1280">
@@ -16985,7 +16985,7 @@
         <v>2027</v>
       </c>
       <c r="D1280">
-        <v>63.92645766604621</v>
+        <v>66.82634263283538</v>
       </c>
     </row>
     <row r="1281">
@@ -16998,7 +16998,7 @@
         <v>2028</v>
       </c>
       <c r="D1281">
-        <v>66.82634260248631</v>
+        <v>69.7262302286284</v>
       </c>
     </row>
     <row r="1282">
@@ -17037,7 +17037,7 @@
         <v>2026</v>
       </c>
       <c r="D1284">
-        <v>11.9516947501864</v>
+        <v>12.17949359946929</v>
       </c>
     </row>
     <row r="1285">
@@ -17050,7 +17050,7 @@
         <v>2027</v>
       </c>
       <c r="D1285">
-        <v>12.12485500957847</v>
+        <v>12.39922150334701</v>
       </c>
     </row>
     <row r="1286">
@@ -17063,7 +17063,7 @@
         <v>2028</v>
       </c>
       <c r="D1286">
-        <v>12.41837758067774</v>
+        <v>12.6764176392169</v>
       </c>
     </row>
     <row r="1287">
@@ -17102,7 +17102,7 @@
         <v>2026</v>
       </c>
       <c r="D1289">
-        <v>11.88985177755145</v>
+        <v>11.8116582215495</v>
       </c>
     </row>
     <row r="1290">
@@ -17115,7 +17115,7 @@
         <v>2027</v>
       </c>
       <c r="D1290">
-        <v>11.81165884524712</v>
+        <v>11.73346347616542</v>
       </c>
     </row>
     <row r="1291">
@@ -17128,7 +17128,7 @@
         <v>2028</v>
       </c>
       <c r="D1291">
-        <v>11.73346334906138</v>
+        <v>11.65526834946923</v>
       </c>
     </row>
     <row r="1292">
@@ -17167,7 +17167,7 @@
         <v>2026</v>
       </c>
       <c r="D1294">
-        <v>23.85712010203849</v>
+        <v>26.28872476972877</v>
       </c>
     </row>
     <row r="1295">
@@ -17180,7 +17180,7 @@
         <v>2027</v>
       </c>
       <c r="D1295">
-        <v>26.29548999080743</v>
+        <v>28.70023373995595</v>
       </c>
     </row>
     <row r="1296">
@@ -17193,7 +17193,7 @@
         <v>2028</v>
       </c>
       <c r="D1296">
-        <v>28.69910062100548</v>
+        <v>31.10834335333174</v>
       </c>
     </row>
     <row r="1297">
@@ -17232,7 +17232,7 @@
         <v>2026</v>
       </c>
       <c r="D1299">
-        <v>81.36847344340562</v>
+        <v>83.46237637801885</v>
       </c>
     </row>
     <row r="1300">
@@ -17245,7 +17245,7 @@
         <v>2027</v>
       </c>
       <c r="D1300">
-        <v>83.44244122784481</v>
+        <v>85.42945598554383</v>
       </c>
     </row>
     <row r="1301">
@@ -17258,7 +17258,7 @@
         <v>2028</v>
       </c>
       <c r="D1301">
-        <v>85.42352607202189</v>
+        <v>87.37874585250297</v>
       </c>
     </row>
     <row r="1302">
@@ -17297,7 +17297,7 @@
         <v>2026</v>
       </c>
       <c r="D1304">
-        <v>87.93101678827567</v>
+        <v>89.92234715914454</v>
       </c>
     </row>
     <row r="1305">
@@ -17310,7 +17310,7 @@
         <v>2027</v>
       </c>
       <c r="D1305">
-        <v>89.92240705435269</v>
+        <v>91.9140767881878</v>
       </c>
     </row>
     <row r="1306">
@@ -17323,7 +17323,7 @@
         <v>2028</v>
       </c>
       <c r="D1306">
-        <v>91.91409312645942</v>
+        <v>93.90585543204594</v>
       </c>
     </row>
     <row r="1307">
@@ -17362,7 +17362,7 @@
         <v>2026</v>
       </c>
       <c r="D1309">
-        <v>52.62465528996461</v>
+        <v>45.84552403039466</v>
       </c>
     </row>
     <row r="1310">
@@ -17375,7 +17375,7 @@
         <v>2027</v>
       </c>
       <c r="D1310">
-        <v>45.84421906653277</v>
+        <v>39.07976059008543</v>
       </c>
     </row>
     <row r="1311">
@@ -17388,7 +17388,7 @@
         <v>2028</v>
       </c>
       <c r="D1311">
-        <v>39.07985912385688</v>
+        <v>32.31429275109058</v>
       </c>
     </row>
   </sheetData>
